--- a/public/exports/19438414.xlsx
+++ b/public/exports/19438414.xlsx
@@ -81,16 +81,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004960</t>
+          <t xml:space="preserve">197867, 197868</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F2">
-        <v>324</v>
+        <v>922</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -131,16 +131,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005056</t>
+          <t xml:space="preserve">199954</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F3">
-        <v>335</v>
+        <v>5288</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -181,7 +181,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005056</t>
+          <t xml:space="preserve">2004960</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -190,7 +190,7 @@
         </is>
       </c>
       <c r="F4">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005056</t>
+          <t xml:space="preserve">2005433</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F5">
-        <v>1479</v>
+        <v>3511</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005433</t>
+          <t xml:space="preserve">2006879</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -290,7 +290,7 @@
         </is>
       </c>
       <c r="F6">
-        <v>3511</v>
+        <v>810</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -336,11 +336,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F7">
-        <v>810</v>
+        <v>375</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006879</t>
+          <t xml:space="preserve">2035146</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F8">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035146</t>
+          <t xml:space="preserve">2036359</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F9">
-        <v>349</v>
+        <v>821</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036359</t>
+          <t xml:space="preserve">2037454</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F10">
-        <v>821</v>
+        <v>2952</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2037454</t>
+          <t xml:space="preserve">204521, 204522</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="F11">
-        <v>2952</v>
+        <v>4044</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2038849</t>
+          <t xml:space="preserve">204523</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F12">
-        <v>3226</v>
+        <v>1490</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069435</t>
+          <t xml:space="preserve">2069611</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="F15">
-        <v>3524</v>
+        <v>445</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069435</t>
+          <t xml:space="preserve">2069718</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>265</v>
+        <v>870</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069435</t>
+          <t xml:space="preserve">2069718</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F17">
-        <v>3551</v>
+        <v>938</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069435</t>
+          <t xml:space="preserve">2072808</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F18">
-        <v>933</v>
+        <v>1003</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069435</t>
+          <t xml:space="preserve">2072808</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F19">
-        <v>716</v>
+        <v>1142</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069611</t>
+          <t xml:space="preserve">7102484</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F20">
-        <v>445</v>
+        <v>618</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069718</t>
+          <t xml:space="preserve">7102491</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F21">
-        <v>870</v>
+        <v>618</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069718</t>
+          <t xml:space="preserve">8042042</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F22">
-        <v>938</v>
+        <v>865</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">8042042</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F23">
-        <v>1654</v>
+        <v>1185</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070356</t>
+          <t xml:space="preserve">8847451</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F24">
-        <v>1281</v>
+        <v>681</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2072808</t>
+          <t xml:space="preserve">8847451</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F25">
-        <v>1003</v>
+        <v>846</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2072808</t>
+          <t xml:space="preserve">8847451</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F26">
-        <v>1142</v>
+        <v>401</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,30 +1331,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">7102484</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="F27">
-        <v>618</v>
+        <v>1654</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200044240</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-01-12</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1381,30 +1381,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">7102491</t>
+          <t xml:space="preserve">711862, 2037126</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F28">
-        <v>618</v>
+        <v>1048</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200044272</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-01-13</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-02-13</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1481,30 +1481,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">711628, 2042860</t>
+          <t xml:space="preserve">8847602</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F30">
-        <v>745</v>
+        <v>489</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-02-13</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1531,30 +1531,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">711862, 2037126</t>
+          <t xml:space="preserve">8847602</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F31">
-        <v>1048</v>
+        <v>1015</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-02-13</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1581,30 +1581,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">8042042</t>
+          <t xml:space="preserve">2042860</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F32">
-        <v>865</v>
+        <v>502</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311029870</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-12-05</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1631,30 +1631,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8042042</t>
+          <t xml:space="preserve">711628, 2042860</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="F33">
-        <v>1185</v>
+        <v>745</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311029906</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-12-05</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1681,30 +1681,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847451</t>
+          <t xml:space="preserve">8847602</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F34">
-        <v>681</v>
+        <v>11783</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311155513</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-01-26</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1731,30 +1731,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847451</t>
+          <t xml:space="preserve">2036708</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F35">
-        <v>846</v>
+        <v>1022</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311191657</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-07-26</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1781,30 +1781,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847451</t>
+          <t xml:space="preserve">2037235</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F36">
-        <v>401</v>
+        <v>685</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311191655</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-07-26</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -1831,30 +1831,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847602</t>
+          <t xml:space="preserve">2071735</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F37">
-        <v>1015</v>
+        <v>285</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311191658</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-07-26</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -1881,25 +1881,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069435</t>
+          <t xml:space="preserve">2072180</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F38">
-        <v>1269</v>
+        <v>447</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024814</t>
+          <t xml:space="preserve">311191661</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-01</t>
+          <t xml:space="preserve">2026-07-26</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000002</t>
+          <t xml:space="preserve">2072552</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F39">
-        <v>1405</v>
+        <v>636</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043001</t>
+          <t xml:space="preserve">311191659</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-15</t>
+          <t xml:space="preserve">2026-07-26</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1981,25 +1981,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847602</t>
+          <t xml:space="preserve">2035660</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F40">
-        <v>489</v>
+        <v>776</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024939</t>
+          <t xml:space="preserve">311191902</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-02-13</t>
+          <t xml:space="preserve">2026-07-27</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2042860</t>
+          <t xml:space="preserve">2037447</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F41">
-        <v>502</v>
+        <v>676</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311029870</t>
+          <t xml:space="preserve">311191957</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-12-05</t>
+          <t xml:space="preserve">2026-07-27</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2081,25 +2081,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8733531</t>
+          <t xml:space="preserve">2037447</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F42">
-        <v>737</v>
+        <v>3140</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311090018</t>
+          <t xml:space="preserve">311191957</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-07</t>
+          <t xml:space="preserve">2026-07-27</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2131,25 +2131,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847602</t>
+          <t xml:space="preserve">2006514</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F43">
-        <v>11783</v>
+        <v>256</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311155513</t>
+          <t xml:space="preserve">311192252</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-26</t>
+          <t xml:space="preserve">2026-07-29</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2181,25 +2181,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036708</t>
+          <t xml:space="preserve">2006514</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F44">
-        <v>1022</v>
+        <v>325</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191657</t>
+          <t xml:space="preserve">311192252</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-26</t>
+          <t xml:space="preserve">2026-07-29</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2037235</t>
+          <t xml:space="preserve">2036747</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="F45">
-        <v>685</v>
+        <v>413</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191655</t>
+          <t xml:space="preserve">311194703</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-26</t>
+          <t xml:space="preserve">2026-08-16</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2071735</t>
+          <t xml:space="preserve">2038903</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="F46">
-        <v>285</v>
+        <v>942</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191658</t>
+          <t xml:space="preserve">311194720</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-26</t>
+          <t xml:space="preserve">2026-08-16</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2072180</t>
+          <t xml:space="preserve">2038912</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2340,16 +2340,16 @@
         </is>
       </c>
       <c r="F47">
-        <v>447</v>
+        <v>1064</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191661</t>
+          <t xml:space="preserve">311194771</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-26</t>
+          <t xml:space="preserve">2026-08-16</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2072552</t>
+          <t xml:space="preserve">2035105</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2390,16 +2390,16 @@
         </is>
       </c>
       <c r="F48">
-        <v>636</v>
+        <v>523</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191659</t>
+          <t xml:space="preserve">311196676</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-26</t>
+          <t xml:space="preserve">2026-08-25</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2431,25 +2431,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8553892</t>
+          <t xml:space="preserve">2002351</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F49">
-        <v>708</v>
+        <v>459</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191753</t>
+          <t xml:space="preserve">311196855</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-26</t>
+          <t xml:space="preserve">2026-08-26</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035660</t>
+          <t xml:space="preserve">8553892</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2490,16 +2490,16 @@
         </is>
       </c>
       <c r="F50">
-        <v>776</v>
+        <v>368</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191902</t>
+          <t xml:space="preserve">311197614</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-27</t>
+          <t xml:space="preserve">2026-08-31</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2531,25 +2531,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2037447</t>
+          <t xml:space="preserve">8553892</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F51">
-        <v>676</v>
+        <v>708</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191957</t>
+          <t xml:space="preserve">311197615</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-27</t>
+          <t xml:space="preserve">2026-08-31</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2037447</t>
+          <t xml:space="preserve">1300011</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2590,16 +2590,16 @@
         </is>
       </c>
       <c r="F52">
-        <v>3140</v>
+        <v>691</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191957</t>
+          <t xml:space="preserve">311198202</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-27</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2631,35 +2631,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006514</t>
+          <t xml:space="preserve">2070447</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F53">
-        <v>256</v>
+        <v>1806</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192252</t>
+          <t xml:space="preserve">311199190</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-29</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2681,35 +2681,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006514</t>
+          <t xml:space="preserve">2070447</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F54">
-        <v>325</v>
+        <v>3927</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192252</t>
+          <t xml:space="preserve">311199269</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-29</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2731,35 +2731,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036747</t>
+          <t xml:space="preserve">2070447</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F55">
-        <v>413</v>
+        <v>728</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311194703</t>
+          <t xml:space="preserve">311199269</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2781,35 +2781,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2038903</t>
+          <t xml:space="preserve">2070447</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F56">
-        <v>942</v>
+        <v>1618</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311194720</t>
+          <t xml:space="preserve">311199269</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2831,35 +2831,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2038912</t>
+          <t xml:space="preserve">8733531</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F57">
-        <v>1064</v>
+        <v>737</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311194771</t>
+          <t xml:space="preserve">311199515</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035105</t>
+          <t xml:space="preserve">2005256</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2890,26 +2890,26 @@
         </is>
       </c>
       <c r="F58">
-        <v>523</v>
+        <v>613</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311196676</t>
+          <t xml:space="preserve">311201173</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25</t>
+          <t xml:space="preserve">2026-09-18</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036431</t>
+          <t xml:space="preserve">2070470</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2940,26 +2940,26 @@
         </is>
       </c>
       <c r="F59">
-        <v>895</v>
+        <v>1075</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311196678</t>
+          <t xml:space="preserve">311201162</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25</t>
+          <t xml:space="preserve">2026-09-18</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002351</t>
+          <t xml:space="preserve">7904671</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2990,26 +2990,26 @@
         </is>
       </c>
       <c r="F60">
-        <v>459</v>
+        <v>498</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311196855</t>
+          <t xml:space="preserve">311201169</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-26</t>
+          <t xml:space="preserve">2026-09-18</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">8553892</t>
+          <t xml:space="preserve">2036778</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3040,26 +3040,26 @@
         </is>
       </c>
       <c r="F61">
-        <v>368</v>
+        <v>1069</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311197614</t>
+          <t xml:space="preserve">311201716</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300011</t>
+          <t xml:space="preserve">2036778</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3090,26 +3090,26 @@
         </is>
       </c>
       <c r="F62">
-        <v>691</v>
+        <v>1186</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311198202</t>
+          <t xml:space="preserve">311201716</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3131,25 +3131,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070447</t>
+          <t xml:space="preserve">2036778</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F63">
-        <v>1806</v>
+        <v>2057</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199190</t>
+          <t xml:space="preserve">311201716</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070447</t>
+          <t xml:space="preserve">2036778</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F64">
-        <v>3927</v>
+        <v>883</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199269</t>
+          <t xml:space="preserve">311201716</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070447</t>
+          <t xml:space="preserve">2036778</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F65">
-        <v>728</v>
+        <v>5759</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199269</t>
+          <t xml:space="preserve">311201716</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070447</t>
+          <t xml:space="preserve">8733531</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F66">
-        <v>1618</v>
+        <v>6246</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199269</t>
+          <t xml:space="preserve">311202581</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,25 +3331,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">10052046</t>
+          <t xml:space="preserve">8733531</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F67">
-        <v>1074</v>
+        <v>644</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200344</t>
+          <t xml:space="preserve">311202581</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-13</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">10052046</t>
+          <t xml:space="preserve">8733531</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F68">
-        <v>600</v>
+        <v>454</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200344</t>
+          <t xml:space="preserve">311202581</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-13</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005256</t>
+          <t xml:space="preserve">2069524</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3440,16 +3440,16 @@
         </is>
       </c>
       <c r="F69">
-        <v>613</v>
+        <v>9626</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201173</t>
+          <t xml:space="preserve">311202814</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-18</t>
+          <t xml:space="preserve">2026-09-26</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070470</t>
+          <t xml:space="preserve">2069524</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F70">
-        <v>1075</v>
+        <v>267</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201162</t>
+          <t xml:space="preserve">311202816</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-18</t>
+          <t xml:space="preserve">2026-09-26</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">7904671</t>
+          <t xml:space="preserve">2069524</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F71">
-        <v>498</v>
+        <v>808</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201169</t>
+          <t xml:space="preserve">311202814</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-18</t>
+          <t xml:space="preserve">2026-09-26</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036778</t>
+          <t xml:space="preserve">8847425</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F72">
-        <v>1069</v>
+        <v>744</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201716</t>
+          <t xml:space="preserve">311203109</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036778</t>
+          <t xml:space="preserve">8847425</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F73">
-        <v>1186</v>
+        <v>697</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201716</t>
+          <t xml:space="preserve">311203227</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036778</t>
+          <t xml:space="preserve">2005606</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74">
-        <v>2057</v>
+        <v>3601</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201716</t>
+          <t xml:space="preserve">311203429</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036778</t>
+          <t xml:space="preserve">2005606</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F75">
-        <v>883</v>
+        <v>858</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201716</t>
+          <t xml:space="preserve">311203429</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036778</t>
+          <t xml:space="preserve">8847425</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F76">
-        <v>5759</v>
+        <v>5441</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201716</t>
+          <t xml:space="preserve">311203641</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">8733531</t>
+          <t xml:space="preserve">8847425</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F77">
-        <v>6246</v>
+        <v>2255</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202581</t>
+          <t xml:space="preserve">311203641</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-25</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">8733531</t>
+          <t xml:space="preserve">7102230</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F78">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202581</t>
+          <t xml:space="preserve">311278723</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-25</t>
+          <t xml:space="preserve">2026-10-04</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,25 +3931,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8733531</t>
+          <t xml:space="preserve">2008702</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F79">
-        <v>454</v>
+        <v>307</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202581</t>
+          <t xml:space="preserve">311204805</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-25</t>
+          <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069524</t>
+          <t xml:space="preserve">2072232</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3990,16 +3990,16 @@
         </is>
       </c>
       <c r="F80">
-        <v>9626</v>
+        <v>654</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202814</t>
+          <t xml:space="preserve">311204794</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-26</t>
+          <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069524</t>
+          <t xml:space="preserve">2004165</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F81">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202816</t>
+          <t xml:space="preserve">311205141</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-26</t>
+          <t xml:space="preserve">2026-10-06</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,25 +4081,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069524</t>
+          <t xml:space="preserve">2004165</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F82">
-        <v>808</v>
+        <v>270</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202814</t>
+          <t xml:space="preserve">311205140</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-26</t>
+          <t xml:space="preserve">2026-10-06</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,25 +4131,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847425</t>
+          <t xml:space="preserve">2072550</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F83">
-        <v>744</v>
+        <v>701</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203109</t>
+          <t xml:space="preserve">311205155</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-10-07</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847425</t>
+          <t xml:space="preserve">2005774</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F84">
-        <v>697</v>
+        <v>316</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203227</t>
+          <t xml:space="preserve">311206074</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-10-12</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005606</t>
+          <t xml:space="preserve">8159434</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4240,16 +4240,16 @@
         </is>
       </c>
       <c r="F85">
-        <v>3601</v>
+        <v>479</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203429</t>
+          <t xml:space="preserve">311206554</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-10-13</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005606</t>
+          <t xml:space="preserve">2005750</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F86">
-        <v>858</v>
+        <v>333</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203429</t>
+          <t xml:space="preserve">311206703</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-10-14</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847425</t>
+          <t xml:space="preserve">2005968</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="F87">
-        <v>5441</v>
+        <v>4371</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203641</t>
+          <t xml:space="preserve">311206763</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-10-14</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,25 +4381,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847425</t>
+          <t xml:space="preserve">2002945</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F88">
-        <v>2255</v>
+        <v>700</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203641</t>
+          <t xml:space="preserve">311206970</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">7102230</t>
+          <t xml:space="preserve">2004758</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4440,16 +4440,16 @@
         </is>
       </c>
       <c r="F89">
-        <v>643</v>
+        <v>601</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278723</t>
+          <t xml:space="preserve">311207210</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-04</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008702</t>
+          <t xml:space="preserve">2006270</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="F90">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311204805</t>
+          <t xml:space="preserve">311207911</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-05</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2072232</t>
+          <t xml:space="preserve">2004800</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4540,16 +4540,16 @@
         </is>
       </c>
       <c r="F91">
-        <v>654</v>
+        <v>273</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311204794</t>
+          <t xml:space="preserve">311208139</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-05</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004165</t>
+          <t xml:space="preserve">2008241</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4590,16 +4590,16 @@
         </is>
       </c>
       <c r="F92">
-        <v>303</v>
+        <v>409</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311205141</t>
+          <t xml:space="preserve">311208141</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-06</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,25 +4631,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004165</t>
+          <t xml:space="preserve">2018968</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F93">
-        <v>270</v>
+        <v>485</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311205140</t>
+          <t xml:space="preserve">311208140</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-06</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2072550</t>
+          <t xml:space="preserve">7632032</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4690,16 +4690,16 @@
         </is>
       </c>
       <c r="F94">
-        <v>701</v>
+        <v>650</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311205155</t>
+          <t xml:space="preserve">311208138</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-07</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,25 +4731,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005774</t>
+          <t xml:space="preserve">2018945</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F95">
-        <v>316</v>
+        <v>672</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206074</t>
+          <t xml:space="preserve">311208347</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-12</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">8159434</t>
+          <t xml:space="preserve">2003860</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="F96">
-        <v>479</v>
+        <v>413</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206554</t>
+          <t xml:space="preserve">311208814</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-13</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005750</t>
+          <t xml:space="preserve">2003860</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F97">
-        <v>333</v>
+        <v>435</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206703</t>
+          <t xml:space="preserve">311208816</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005968</t>
+          <t xml:space="preserve">2068313</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4890,16 +4890,16 @@
         </is>
       </c>
       <c r="F98">
-        <v>4371</v>
+        <v>445</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206763</t>
+          <t xml:space="preserve">311209724</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002945</t>
+          <t xml:space="preserve">2002904</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4940,16 +4940,16 @@
         </is>
       </c>
       <c r="F99">
-        <v>700</v>
+        <v>769</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206970</t>
+          <t xml:space="preserve">311209896</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-11-01</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004758</t>
+          <t xml:space="preserve">2036359</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4990,16 +4990,16 @@
         </is>
       </c>
       <c r="F100">
-        <v>601</v>
+        <v>916</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207210</t>
+          <t xml:space="preserve">311209732</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-11-01</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006270</t>
+          <t xml:space="preserve">2068091</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5040,16 +5040,16 @@
         </is>
       </c>
       <c r="F101">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207911</t>
+          <t xml:space="preserve">311210319</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-11-03</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004800</t>
+          <t xml:space="preserve">2066536</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5090,16 +5090,16 @@
         </is>
       </c>
       <c r="F102">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208139</t>
+          <t xml:space="preserve">311210702</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008241</t>
+          <t xml:space="preserve">2067876</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F103">
-        <v>409</v>
+        <v>306</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208141</t>
+          <t xml:space="preserve">311210734</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018968</t>
+          <t xml:space="preserve">2068762</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5190,16 +5190,16 @@
         </is>
       </c>
       <c r="F104">
-        <v>485</v>
+        <v>321</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208140</t>
+          <t xml:space="preserve">311210703</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">7632032</t>
+          <t xml:space="preserve">2068592</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="F105">
-        <v>650</v>
+        <v>321</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208138</t>
+          <t xml:space="preserve">311211009</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,25 +5281,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018945</t>
+          <t xml:space="preserve">7102489</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F106">
-        <v>672</v>
+        <v>636</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208354</t>
+          <t xml:space="preserve">311211003</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2003860</t>
+          <t xml:space="preserve">10052046</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5340,16 +5340,16 @@
         </is>
       </c>
       <c r="F107">
-        <v>413</v>
+        <v>1074</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208814</t>
+          <t xml:space="preserve">311211872</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2003860</t>
+          <t xml:space="preserve">10052046</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F108">
-        <v>435</v>
+        <v>600</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208816</t>
+          <t xml:space="preserve">311211872</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068313</t>
+          <t xml:space="preserve">2004887</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5440,16 +5440,16 @@
         </is>
       </c>
       <c r="F109">
-        <v>445</v>
+        <v>510</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209724</t>
+          <t xml:space="preserve">311211852</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002904</t>
+          <t xml:space="preserve">9110623</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5490,16 +5490,16 @@
         </is>
       </c>
       <c r="F110">
-        <v>769</v>
+        <v>891</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209896</t>
+          <t xml:space="preserve">311211974</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-01</t>
+          <t xml:space="preserve">2026-11-12</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036359</t>
+          <t xml:space="preserve">2065746</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5540,16 +5540,16 @@
         </is>
       </c>
       <c r="F111">
-        <v>916</v>
+        <v>308</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209732</t>
+          <t xml:space="preserve">311211980</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-01</t>
+          <t xml:space="preserve">2026-11-13</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068091</t>
+          <t xml:space="preserve">2018920</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="F112">
-        <v>284</v>
+        <v>582</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210319</t>
+          <t xml:space="preserve">311212242</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-03</t>
+          <t xml:space="preserve">2026-11-14</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2066536</t>
+          <t xml:space="preserve">2000399</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5640,16 +5640,16 @@
         </is>
       </c>
       <c r="F113">
-        <v>266</v>
+        <v>557</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210702</t>
+          <t xml:space="preserve">311214238</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2067876</t>
+          <t xml:space="preserve">2000399</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="F114">
-        <v>306</v>
+        <v>384</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210734</t>
+          <t xml:space="preserve">311214238</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068762</t>
+          <t xml:space="preserve">2008230</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5740,16 +5740,16 @@
         </is>
       </c>
       <c r="F115">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210703</t>
+          <t xml:space="preserve">311214235</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068592</t>
+          <t xml:space="preserve">2068785</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="F116">
-        <v>321</v>
+        <v>859</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211009</t>
+          <t xml:space="preserve">311214236</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,25 +5831,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">7102489</t>
+          <t xml:space="preserve">2073075</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F117">
-        <v>636</v>
+        <v>684</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211003</t>
+          <t xml:space="preserve">311214237</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004887</t>
+          <t xml:space="preserve">2006242</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5890,16 +5890,16 @@
         </is>
       </c>
       <c r="F118">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211852</t>
+          <t xml:space="preserve">311214517</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,25 +5931,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9110623</t>
+          <t xml:space="preserve">2006242</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F119">
-        <v>891</v>
+        <v>322</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211974</t>
+          <t xml:space="preserve">311214517</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-12</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5981,25 +5981,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2065746</t>
+          <t xml:space="preserve">2006242</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F120">
-        <v>308</v>
+        <v>637</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211980</t>
+          <t xml:space="preserve">311214517</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-13</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018920</t>
+          <t xml:space="preserve">2008955</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="F121">
-        <v>582</v>
+        <v>400</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212242</t>
+          <t xml:space="preserve">311214489</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-14</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,25 +6081,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000399</t>
+          <t xml:space="preserve">2008955</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F122">
-        <v>557</v>
+        <v>410</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214238</t>
+          <t xml:space="preserve">311214489</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,25 +6131,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000399</t>
+          <t xml:space="preserve">2008955</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F123">
-        <v>384</v>
+        <v>424</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214238</t>
+          <t xml:space="preserve">311214489</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,25 +6181,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008230</t>
+          <t xml:space="preserve">2008955</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F124">
-        <v>324</v>
+        <v>540</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214235</t>
+          <t xml:space="preserve">311214489</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,25 +6231,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068785</t>
+          <t xml:space="preserve">2008955</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F125">
-        <v>859</v>
+        <v>584</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214236</t>
+          <t xml:space="preserve">311214489</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,25 +6281,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2073075</t>
+          <t xml:space="preserve">2008955</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F126">
-        <v>684</v>
+        <v>520</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214237</t>
+          <t xml:space="preserve">311214489</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847600</t>
+          <t xml:space="preserve">2069612</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="F127">
-        <v>1170</v>
+        <v>1702</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214244</t>
+          <t xml:space="preserve">311215778</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-25</t>
+          <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6381,25 +6381,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006242</t>
+          <t xml:space="preserve">2069612</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F128">
-        <v>300</v>
+        <v>1702</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214517</t>
+          <t xml:space="preserve">311215778</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,25 +6431,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006242</t>
+          <t xml:space="preserve">2069612</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F129">
-        <v>322</v>
+        <v>1702</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214517</t>
+          <t xml:space="preserve">311215778</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,25 +6481,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006242</t>
+          <t xml:space="preserve">2069694</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F130">
-        <v>637</v>
+        <v>1920</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214517</t>
+          <t xml:space="preserve">311215775</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,25 +6531,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008955</t>
+          <t xml:space="preserve">2069694</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F131">
-        <v>400</v>
+        <v>1920</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214489</t>
+          <t xml:space="preserve">311215775</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008955</t>
+          <t xml:space="preserve">2069698</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F132">
-        <v>410</v>
+        <v>1536</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214489</t>
+          <t xml:space="preserve">311215779</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,25 +6631,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008955</t>
+          <t xml:space="preserve">2069698</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F133">
-        <v>424</v>
+        <v>1536</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214489</t>
+          <t xml:space="preserve">311215779</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,25 +6681,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008955</t>
+          <t xml:space="preserve">2069839</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F134">
-        <v>540</v>
+        <v>1020</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214489</t>
+          <t xml:space="preserve">311215887</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-12-04</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,25 +6731,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008955</t>
+          <t xml:space="preserve">7102138</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F135">
-        <v>584</v>
+        <v>464</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214489</t>
+          <t xml:space="preserve">311215880</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-12-04</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008955</t>
+          <t xml:space="preserve">8286535</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F136">
-        <v>520</v>
+        <v>433</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214489</t>
+          <t xml:space="preserve">311215889</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-12-04</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069612</t>
+          <t xml:space="preserve">2069305</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -6840,16 +6840,16 @@
         </is>
       </c>
       <c r="F137">
-        <v>1702</v>
+        <v>580</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215778</t>
+          <t xml:space="preserve">311215975</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-02</t>
+          <t xml:space="preserve">2026-12-05</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,25 +6881,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069612</t>
+          <t xml:space="preserve">2069545</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F138">
-        <v>1702</v>
+        <v>432</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215778</t>
+          <t xml:space="preserve">311217121</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-02</t>
+          <t xml:space="preserve">2026-12-12</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,25 +6931,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069612</t>
+          <t xml:space="preserve">2069552</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F139">
-        <v>1702</v>
+        <v>429</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215778</t>
+          <t xml:space="preserve">311217259</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-02</t>
+          <t xml:space="preserve">2026-12-12</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069694</t>
+          <t xml:space="preserve">2068782</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6990,16 +6990,16 @@
         </is>
       </c>
       <c r="F140">
-        <v>1920</v>
+        <v>708</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215775</t>
+          <t xml:space="preserve">311217268</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-02</t>
+          <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069694</t>
+          <t xml:space="preserve">2069583</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F141">
-        <v>1920</v>
+        <v>396</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215775</t>
+          <t xml:space="preserve">311217266</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-02</t>
+          <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069698</t>
+          <t xml:space="preserve">2070043</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7090,16 +7090,16 @@
         </is>
       </c>
       <c r="F142">
-        <v>1536</v>
+        <v>1270</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215779</t>
+          <t xml:space="preserve">311218402</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-02</t>
+          <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,25 +7131,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069698</t>
+          <t xml:space="preserve">2069435</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F143">
-        <v>1536</v>
+        <v>3524</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215779</t>
+          <t xml:space="preserve">311220163</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-02</t>
+          <t xml:space="preserve">2026-12-30</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069839</t>
+          <t xml:space="preserve">2069435</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F144">
-        <v>1020</v>
+        <v>265</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215887</t>
+          <t xml:space="preserve">311220163</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-04</t>
+          <t xml:space="preserve">2026-12-30</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7231,25 +7231,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7102138</t>
+          <t xml:space="preserve">2069435</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F145">
-        <v>464</v>
+        <v>3551</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215880</t>
+          <t xml:space="preserve">311220163</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-04</t>
+          <t xml:space="preserve">2026-12-30</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,25 +7281,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">8286535</t>
+          <t xml:space="preserve">2069435</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F146">
-        <v>433</v>
+        <v>933</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215889</t>
+          <t xml:space="preserve">311220163</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-04</t>
+          <t xml:space="preserve">2026-12-30</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,25 +7331,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069305</t>
+          <t xml:space="preserve">2069435</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F147">
-        <v>580</v>
+        <v>716</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215975</t>
+          <t xml:space="preserve">311220163</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-05</t>
+          <t xml:space="preserve">2026-12-30</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069545</t>
+          <t xml:space="preserve">2069435</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F148">
-        <v>432</v>
+        <v>1269</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217121</t>
+          <t xml:space="preserve">311220163</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-12</t>
+          <t xml:space="preserve">2026-12-30</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069552</t>
+          <t xml:space="preserve">2006876</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -7440,16 +7440,16 @@
         </is>
       </c>
       <c r="F149">
-        <v>429</v>
+        <v>9347</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217259</t>
+          <t xml:space="preserve">311220175</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-12</t>
+          <t xml:space="preserve">2026-12-31</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068782</t>
+          <t xml:space="preserve">2006876</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F150">
-        <v>708</v>
+        <v>3535</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217268</t>
+          <t xml:space="preserve">311220175</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-13</t>
+          <t xml:space="preserve">2026-12-31</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,25 +7531,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069583</t>
+          <t xml:space="preserve">2006876</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F151">
-        <v>396</v>
+        <v>4974</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217266</t>
+          <t xml:space="preserve">311220175</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-13</t>
+          <t xml:space="preserve">2026-12-31</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,25 +7581,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">204523</t>
+          <t xml:space="preserve">2006876</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F152">
-        <v>1490</v>
+        <v>1071</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217912</t>
+          <t xml:space="preserve">311220175</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-15</t>
+          <t xml:space="preserve">2026-12-31</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,25 +7631,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">204521, 204522</t>
+          <t xml:space="preserve">2005642</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F153">
-        <v>4044</v>
+        <v>4984</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218075</t>
+          <t xml:space="preserve">311232130</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070043</t>
+          <t xml:space="preserve">2006712</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -7690,16 +7690,16 @@
         </is>
       </c>
       <c r="F154">
-        <v>1270</v>
+        <v>3975</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218402</t>
+          <t xml:space="preserve">311232713</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-18</t>
+          <t xml:space="preserve">2027-03-08</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,25 +7731,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070356</t>
+          <t xml:space="preserve">2006712</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F155">
-        <v>3922</v>
+        <v>727</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218511</t>
+          <t xml:space="preserve">311232714</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2027-03-08</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006876</t>
+          <t xml:space="preserve">10052046</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F156">
-        <v>9347</v>
+        <v>1404</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220175</t>
+          <t xml:space="preserve">311236053</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-31</t>
+          <t xml:space="preserve">2027-03-23</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,25 +7831,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006876</t>
+          <t xml:space="preserve">8917277</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F157">
-        <v>3535</v>
+        <v>8434</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220175</t>
+          <t xml:space="preserve">311236293</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-31</t>
+          <t xml:space="preserve">2027-03-23</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006876</t>
+          <t xml:space="preserve">9305089</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F158">
-        <v>4974</v>
+        <v>2193</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220175</t>
+          <t xml:space="preserve">311236656</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-31</t>
+          <t xml:space="preserve">2027-03-25</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7931,25 +7931,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006876</t>
+          <t xml:space="preserve">2038916</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F159">
-        <v>1071</v>
+        <v>706</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220175</t>
+          <t xml:space="preserve">311237048</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-31</t>
+          <t xml:space="preserve">2027-03-27</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005642</t>
+          <t xml:space="preserve">2006875</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7990,16 +7990,16 @@
         </is>
       </c>
       <c r="F160">
-        <v>4984</v>
+        <v>1635</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311232130</t>
+          <t xml:space="preserve">311242890</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-05</t>
+          <t xml:space="preserve">2027-04-25</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006712</t>
+          <t xml:space="preserve">1300011</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8040,16 +8040,16 @@
         </is>
       </c>
       <c r="F161">
-        <v>3975</v>
+        <v>400</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311232713</t>
+          <t xml:space="preserve">311243628</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-08</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006712</t>
+          <t xml:space="preserve">2001527</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F162">
-        <v>727</v>
+        <v>759</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311232714</t>
+          <t xml:space="preserve">311243656</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-08</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,25 +8131,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">10052046</t>
+          <t xml:space="preserve">9305089</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F163">
-        <v>1404</v>
+        <v>1149</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236053</t>
+          <t xml:space="preserve">311243583</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-23</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,25 +8181,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">8917277</t>
+          <t xml:space="preserve">9305089</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F164">
-        <v>8434</v>
+        <v>709</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236293</t>
+          <t xml:space="preserve">311243583</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-23</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8236,20 +8236,20 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F165">
-        <v>2193</v>
+        <v>701</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236656</t>
+          <t xml:space="preserve">311243583</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-25</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,25 +8281,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2038916</t>
+          <t xml:space="preserve">9305089</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F166">
-        <v>706</v>
+        <v>2692</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311237048</t>
+          <t xml:space="preserve">311243583</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-27</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,25 +8331,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006875</t>
+          <t xml:space="preserve">9305089</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F167">
-        <v>1635</v>
+        <v>536</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242890</t>
+          <t xml:space="preserve">311243583</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-25</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300011</t>
+          <t xml:space="preserve">2001352</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -8390,16 +8390,16 @@
         </is>
       </c>
       <c r="F168">
-        <v>400</v>
+        <v>5437</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243628</t>
+          <t xml:space="preserve">311244012</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-04-28</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,25 +8431,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2001527</t>
+          <t xml:space="preserve">2001352</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F169">
-        <v>759</v>
+        <v>785</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243656</t>
+          <t xml:space="preserve">311244012</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-04-28</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,25 +8481,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305089</t>
+          <t xml:space="preserve">2001352</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F170">
-        <v>1149</v>
+        <v>517</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243583</t>
+          <t xml:space="preserve">311244012</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-04-28</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,25 +8531,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305089</t>
+          <t xml:space="preserve">2069384</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F171">
-        <v>709</v>
+        <v>782</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243583</t>
+          <t xml:space="preserve">311245806</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-05-07</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305089</t>
+          <t xml:space="preserve">2002588</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F172">
-        <v>701</v>
+        <v>750</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243583</t>
+          <t xml:space="preserve">311246147</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,25 +8631,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305089</t>
+          <t xml:space="preserve">2004925</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F173">
-        <v>2692</v>
+        <v>546</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243583</t>
+          <t xml:space="preserve">311246229</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,25 +8681,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305089</t>
+          <t xml:space="preserve">2006002</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F174">
-        <v>536</v>
+        <v>472</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243583</t>
+          <t xml:space="preserve">311246339</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2001352</t>
+          <t xml:space="preserve">2038849</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -8740,16 +8740,16 @@
         </is>
       </c>
       <c r="F175">
-        <v>5437</v>
+        <v>5742</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311244012</t>
+          <t xml:space="preserve">311246445</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-28</t>
+          <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8781,25 +8781,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2001352</t>
+          <t xml:space="preserve">2038849</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F176">
-        <v>785</v>
+        <v>3226</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311244012</t>
+          <t xml:space="preserve">311246446</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-28</t>
+          <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,25 +8831,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2001352</t>
+          <t xml:space="preserve">9305092</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F177">
-        <v>517</v>
+        <v>1579</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311244012</t>
+          <t xml:space="preserve">311246144</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-28</t>
+          <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8881,25 +8881,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069384</t>
+          <t xml:space="preserve">9305092</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F178">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311245806</t>
+          <t xml:space="preserve">311246144</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-07</t>
+          <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8931,20 +8931,20 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002588</t>
+          <t xml:space="preserve">9305092</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F179">
-        <v>750</v>
+        <v>362</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246147</t>
+          <t xml:space="preserve">311246144</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8981,20 +8981,20 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004925</t>
+          <t xml:space="preserve">9305092</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F180">
-        <v>546</v>
+        <v>256</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246229</t>
+          <t xml:space="preserve">311246144</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -9031,25 +9031,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006002</t>
+          <t xml:space="preserve">2069531</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F181">
-        <v>472</v>
+        <v>373</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246339</t>
+          <t xml:space="preserve">311246563</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-09</t>
+          <t xml:space="preserve">2027-05-10</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2038849</t>
+          <t xml:space="preserve">2006002</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -9090,16 +9090,16 @@
         </is>
       </c>
       <c r="F182">
-        <v>5742</v>
+        <v>702</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246445</t>
+          <t xml:space="preserve">311246796</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-09</t>
+          <t xml:space="preserve">2027-05-11</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305092</t>
+          <t xml:space="preserve">2072808</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -9140,16 +9140,16 @@
         </is>
       </c>
       <c r="F183">
-        <v>1579</v>
+        <v>1207</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246144</t>
+          <t xml:space="preserve">311248853</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-09</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,25 +9181,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305092</t>
+          <t xml:space="preserve">8067646</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F184">
-        <v>783</v>
+        <v>750</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246144</t>
+          <t xml:space="preserve">311248917</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-09</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9236,20 +9236,20 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F185">
-        <v>362</v>
+        <v>1061</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246144</t>
+          <t xml:space="preserve">311249330</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-09</t>
+          <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9286,20 +9286,20 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F186">
-        <v>256</v>
+        <v>831</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246144</t>
+          <t xml:space="preserve">311249281</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-09</t>
+          <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9331,25 +9331,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">199954</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F187">
-        <v>5288</v>
+        <v>287</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246755</t>
+          <t xml:space="preserve">311251574</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-10</t>
+          <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069531</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F188">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246563</t>
+          <t xml:space="preserve">311251574</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-10</t>
+          <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9431,25 +9431,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006002</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F189">
-        <v>702</v>
+        <v>373</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246796</t>
+          <t xml:space="preserve">311251574</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-11</t>
+          <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9481,25 +9481,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2072808</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F190">
-        <v>1207</v>
+        <v>373</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248853</t>
+          <t xml:space="preserve">311251574</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9531,25 +9531,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">8067646</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F191">
-        <v>750</v>
+        <v>373</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248917</t>
+          <t xml:space="preserve">311251574</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9581,25 +9581,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305092</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F192">
-        <v>1061</v>
+        <v>389</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311249330</t>
+          <t xml:space="preserve">311251574</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-23</t>
+          <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9631,25 +9631,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305092</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F193">
-        <v>831</v>
+        <v>1119</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311249281</t>
+          <t xml:space="preserve">311251715</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-23</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9686,20 +9686,20 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F194">
-        <v>287</v>
+        <v>408</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251574</t>
+          <t xml:space="preserve">311251715</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-02</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9736,20 +9736,20 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F195">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251574</t>
+          <t xml:space="preserve">311251715</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-02</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9786,20 +9786,20 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F196">
-        <v>373</v>
+        <v>405</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251574</t>
+          <t xml:space="preserve">311251715</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-02</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9836,20 +9836,20 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F197">
-        <v>373</v>
+        <v>404</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251574</t>
+          <t xml:space="preserve">311251715</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-02</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9886,20 +9886,20 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F198">
-        <v>373</v>
+        <v>405</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251574</t>
+          <t xml:space="preserve">311251715</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-02</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9936,20 +9936,20 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F199">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251574</t>
+          <t xml:space="preserve">311251715</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-02</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">2002621</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -9990,16 +9990,16 @@
         </is>
       </c>
       <c r="F200">
-        <v>1119</v>
+        <v>12354</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251715</t>
+          <t xml:space="preserve">311252789</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2027-06-09</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10031,25 +10031,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">2069701</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F201">
-        <v>408</v>
+        <v>1603</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251715</t>
+          <t xml:space="preserve">311295878</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2028-02-02</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10081,25 +10081,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">2069701</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F202">
-        <v>408</v>
+        <v>286</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251715</t>
+          <t xml:space="preserve">311295879</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2028-02-02</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">2069701</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -10140,16 +10140,16 @@
         </is>
       </c>
       <c r="F203">
-        <v>405</v>
+        <v>980</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251715</t>
+          <t xml:space="preserve">311295881</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2028-02-02</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10181,25 +10181,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">8042042</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F204">
-        <v>404</v>
+        <v>6128</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251715</t>
+          <t xml:space="preserve">311298255</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2028-02-17</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10231,25 +10231,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">8042042</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F205">
-        <v>405</v>
+        <v>1297</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251715</t>
+          <t xml:space="preserve">311298255</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2028-02-17</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10281,25 +10281,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">8042042</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F206">
-        <v>405</v>
+        <v>1534</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251715</t>
+          <t xml:space="preserve">311298256</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2028-02-17</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -10331,25 +10331,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002621</t>
+          <t xml:space="preserve">1300936</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F207">
-        <v>12354</v>
+        <v>966</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252789</t>
+          <t xml:space="preserve">311302882</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-09</t>
+          <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10381,25 +10381,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005056</t>
+          <t xml:space="preserve">8847600</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F208">
-        <v>394</v>
+        <v>1170</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294890</t>
+          <t xml:space="preserve">311303245</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-29</t>
+          <t xml:space="preserve">2028-03-16</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069701</t>
+          <t xml:space="preserve">2036431</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -10440,16 +10440,16 @@
         </is>
       </c>
       <c r="F209">
-        <v>1603</v>
+        <v>895</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295878</t>
+          <t xml:space="preserve">311303980</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-02</t>
+          <t xml:space="preserve">2028-03-20</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10481,25 +10481,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069701</t>
+          <t xml:space="preserve">2036994</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F210">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295879</t>
+          <t xml:space="preserve">311304249</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-02</t>
+          <t xml:space="preserve">2028-03-21</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10526,30 +10526,30 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t xml:space="preserve">157</t>
+          <t xml:space="preserve">210</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069701</t>
+          <t xml:space="preserve">9156756</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F211">
-        <v>980</v>
+        <v>3840</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295881</t>
+          <t xml:space="preserve">311306645</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-02</t>
+          <t xml:space="preserve">2028-04-05</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10581,25 +10581,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">8042042</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F212">
-        <v>6128</v>
+        <v>2455</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298255</t>
+          <t xml:space="preserve">311387113</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-17</t>
+          <t xml:space="preserve">2029-07-05</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10631,25 +10631,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">8042042</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F213">
-        <v>1297</v>
+        <v>2046</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298255</t>
+          <t xml:space="preserve">311584847</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-17</t>
+          <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10681,25 +10681,25 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">8042042</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F214">
-        <v>1534</v>
+        <v>2051</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298256</t>
+          <t xml:space="preserve">311584848</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-17</t>
+          <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10731,25 +10731,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300936</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F215">
-        <v>966</v>
+        <v>572</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311302882</t>
+          <t xml:space="preserve">311391980</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-15</t>
+          <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10781,25 +10781,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036994</t>
+          <t xml:space="preserve">2000002</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F216">
-        <v>263</v>
+        <v>1405</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311304249</t>
+          <t xml:space="preserve">311461983</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-21</t>
+          <t xml:space="preserve">2030-09-18</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t xml:space="preserve">210</t>
+          <t xml:space="preserve">157</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">9156756</t>
+          <t xml:space="preserve">2070356</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -10840,16 +10840,16 @@
         </is>
       </c>
       <c r="F217">
-        <v>3840</v>
+        <v>3922</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306645</t>
+          <t xml:space="preserve">311515578</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-05</t>
+          <t xml:space="preserve">2031-04-26</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10881,25 +10881,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">2070356</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F218">
-        <v>2455</v>
+        <v>1281</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311387113</t>
+          <t xml:space="preserve">311515578</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-05</t>
+          <t xml:space="preserve">2031-04-26</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10931,25 +10931,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">2070356</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F219">
-        <v>2046</v>
+        <v>636</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584847</t>
+          <t xml:space="preserve">311526742</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-08</t>
+          <t xml:space="preserve">2031-06-09</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10981,25 +10981,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">2068210</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F220">
-        <v>2051</v>
+        <v>566</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584848</t>
+          <t xml:space="preserve">311552980</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-08</t>
+          <t xml:space="preserve">2031-10-05</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -11031,25 +11031,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">2068262</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F221">
-        <v>572</v>
+        <v>506</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391980</t>
+          <t xml:space="preserve">311556816</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-08</t>
+          <t xml:space="preserve">2031-10-21</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -11081,25 +11081,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070356</t>
+          <t xml:space="preserve">2068330</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F222">
-        <v>636</v>
+        <v>388</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526742</t>
+          <t xml:space="preserve">311556838</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-09</t>
+          <t xml:space="preserve">2031-10-21</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -11131,25 +11131,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068210</t>
+          <t xml:space="preserve">2068330</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F223">
-        <v>566</v>
+        <v>290</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552980</t>
+          <t xml:space="preserve">311556838</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-05</t>
+          <t xml:space="preserve">2031-10-21</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -11181,20 +11181,20 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068262</t>
+          <t xml:space="preserve">2068330</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F224">
-        <v>506</v>
+        <v>580</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556816</t>
+          <t xml:space="preserve">311556838</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -11236,11 +11236,11 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F225">
-        <v>388</v>
+        <v>302</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -11281,25 +11281,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068330</t>
+          <t xml:space="preserve">2069534</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F226">
-        <v>290</v>
+        <v>2580</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556838</t>
+          <t xml:space="preserve">311559143</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-21</t>
+          <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068330</t>
+          <t xml:space="preserve">2069714</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -11340,16 +11340,16 @@
         </is>
       </c>
       <c r="F227">
-        <v>580</v>
+        <v>870</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556838</t>
+          <t xml:space="preserve">311559292</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-21</t>
+          <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068330</t>
+          <t xml:space="preserve">2069714</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -11390,16 +11390,16 @@
         </is>
       </c>
       <c r="F228">
-        <v>302</v>
+        <v>870</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556838</t>
+          <t xml:space="preserve">311559292</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-21</t>
+          <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -11431,20 +11431,20 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069534</t>
+          <t xml:space="preserve">2069714</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F229">
-        <v>2580</v>
+        <v>888</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559143</t>
+          <t xml:space="preserve">311559292</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -11481,25 +11481,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069714</t>
+          <t xml:space="preserve">1300936</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F230">
-        <v>870</v>
+        <v>4249</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559292</t>
+          <t xml:space="preserve">311565422</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-02</t>
+          <t xml:space="preserve">2031-12-01</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -11531,25 +11531,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069714</t>
+          <t xml:space="preserve">1300936</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F231">
-        <v>870</v>
+        <v>306</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559292</t>
+          <t xml:space="preserve">311565462</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-02</t>
+          <t xml:space="preserve">2031-12-01</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -11581,25 +11581,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069714</t>
+          <t xml:space="preserve">2003344</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F232">
-        <v>888</v>
+        <v>1755</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559292</t>
+          <t xml:space="preserve">311568018</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-02</t>
+          <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300936</t>
+          <t xml:space="preserve">2036292</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -11640,16 +11640,16 @@
         </is>
       </c>
       <c r="F233">
-        <v>4249</v>
+        <v>3539</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311565422</t>
+          <t xml:space="preserve">311569171</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-01</t>
+          <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -11681,25 +11681,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300936</t>
+          <t xml:space="preserve">2037126</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F234">
-        <v>306</v>
+        <v>2236</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311565462</t>
+          <t xml:space="preserve">311569166</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-01</t>
+          <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -11731,25 +11731,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2003344</t>
+          <t xml:space="preserve">2037126</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F235">
-        <v>1755</v>
+        <v>913</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568018</t>
+          <t xml:space="preserve">311569166</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -11781,20 +11781,20 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036292</t>
+          <t xml:space="preserve">2037126</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F236">
-        <v>3539</v>
+        <v>1810</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569171</t>
+          <t xml:space="preserve">311569166</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -11836,11 +11836,11 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F237">
-        <v>2236</v>
+        <v>820</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2037126</t>
+          <t xml:space="preserve">2005056</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -11890,16 +11890,16 @@
         </is>
       </c>
       <c r="F238">
-        <v>913</v>
+        <v>394</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569166</t>
+          <t xml:space="preserve">311569817</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-21</t>
+          <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -11931,25 +11931,25 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2037126</t>
+          <t xml:space="preserve">2005056</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F239">
-        <v>1810</v>
+        <v>335</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569166</t>
+          <t xml:space="preserve">311569817</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-21</t>
+          <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -11981,25 +11981,25 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2037126</t>
+          <t xml:space="preserve">2005056</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F240">
-        <v>820</v>
+        <v>307</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569166</t>
+          <t xml:space="preserve">311569817</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-21</t>
+          <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -12031,20 +12031,20 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070356</t>
+          <t xml:space="preserve">2005056</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F241">
-        <v>1717</v>
+        <v>1479</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569804</t>
+          <t xml:space="preserve">311569817</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -12081,25 +12081,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005056</t>
+          <t xml:space="preserve">2070356</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F242">
-        <v>927</v>
+        <v>1717</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570312</t>
+          <t xml:space="preserve">311569804</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-03</t>
+          <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -12131,25 +12131,25 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847602</t>
+          <t xml:space="preserve">2005056</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F243">
-        <v>650</v>
+        <v>927</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574868</t>
+          <t xml:space="preserve">311570312</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-26</t>
+          <t xml:space="preserve">2032-01-03</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -12186,11 +12186,11 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F244">
-        <v>4863</v>
+        <v>650</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -12236,20 +12236,20 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F245">
-        <v>1010</v>
+        <v>4863</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575200</t>
+          <t xml:space="preserve">311574868</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-27</t>
+          <t xml:space="preserve">2032-01-26</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -12281,25 +12281,25 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">8847602</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t xml:space="preserve">89</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F246">
-        <v>2051</v>
+        <v>1010</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584797</t>
+          <t xml:space="preserve">311575200</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-14</t>
+          <t xml:space="preserve">2032-01-27</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -12336,15 +12336,15 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">89</t>
         </is>
       </c>
       <c r="F247">
-        <v>2046</v>
+        <v>2051</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584799</t>
+          <t xml:space="preserve">311584797</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -12386,15 +12386,15 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">91</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
       <c r="F248">
-        <v>2051</v>
+        <v>2046</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584803</t>
+          <t xml:space="preserve">311584799</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -12431,25 +12431,25 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2037271</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">91</t>
         </is>
       </c>
       <c r="F249">
-        <v>1161</v>
+        <v>2051</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590761</t>
+          <t xml:space="preserve">311584803</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-05</t>
+          <t xml:space="preserve">2032-03-14</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -12481,25 +12481,25 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2067880</t>
+          <t xml:space="preserve">2037271</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F250">
-        <v>6480</v>
+        <v>1161</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598275</t>
+          <t xml:space="preserve">311590761</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-06</t>
+          <t xml:space="preserve">2032-04-05</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -12531,25 +12531,25 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847602</t>
+          <t xml:space="preserve">2067880</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F251">
-        <v>3780</v>
+        <v>6480</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311603147</t>
+          <t xml:space="preserve">311598275</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-25</t>
+          <t xml:space="preserve">2032-05-06</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -12581,25 +12581,25 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2042860</t>
+          <t xml:space="preserve">8847602</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F252">
-        <v>575</v>
+        <v>3780</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679358</t>
+          <t xml:space="preserve">311603147</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2032-05-25</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -12631,25 +12631,25 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005284</t>
+          <t xml:space="preserve">2042860</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="F253">
-        <v>1582</v>
+        <v>575</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712629</t>
+          <t xml:space="preserve">311679358</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-05</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2067876</t>
+          <t xml:space="preserve">2005284</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -12690,11 +12690,11 @@
         </is>
       </c>
       <c r="F254">
-        <v>735</v>
+        <v>1582</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712640</t>
+          <t xml:space="preserve">311712629</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">197867, 197868</t>
+          <t xml:space="preserve">2067876</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -12740,16 +12740,16 @@
         </is>
       </c>
       <c r="F255">
-        <v>922</v>
+        <v>735</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311716715</t>
+          <t xml:space="preserve">311712640</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-23</t>
+          <t xml:space="preserve">2033-10-05</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">

--- a/public/exports/19438414.xlsx
+++ b/public/exports/19438414.xlsx
@@ -91,17 +91,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordrup Vænge 122</t>
+          <t xml:space="preserve">Brogårdsvej 85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197867, 197868</t>
+          <t xml:space="preserve">2069611</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -110,7 +110,7 @@
         </is>
       </c>
       <c r="H2">
-        <v>922</v>
+        <v>445</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndersøvej 41A</t>
+          <t xml:space="preserve">Ermelundsvej 41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199954</t>
+          <t xml:space="preserve">2068262</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H3">
-        <v>5288</v>
+        <v>920</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Onsgårdsvej 18</t>
+          <t xml:space="preserve">Gersonsvej 41</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,16 +221,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004960</t>
+          <t xml:space="preserve">2005433</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H4">
-        <v>324</v>
+        <v>3511</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gersonsvej 41</t>
+          <t xml:space="preserve">Grønnevænge 14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005433</t>
+          <t xml:space="preserve">2036359</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H5">
-        <v>3511</v>
+        <v>821</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,26 +331,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tonysvej 44A</t>
+          <t xml:space="preserve">Hellerupvej 18A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006879</t>
+          <t xml:space="preserve">8042042</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H6">
-        <v>810</v>
+        <v>865</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tonysvej 44A</t>
+          <t xml:space="preserve">Hellerupvej 18B</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006879</t>
+          <t xml:space="preserve">8042042</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H7">
-        <v>375</v>
+        <v>1185</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 144A</t>
+          <t xml:space="preserve">Jægersborg Alle 172</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035146</t>
+          <t xml:space="preserve">2068340</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H8">
-        <v>349</v>
+        <v>1536</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,26 +511,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevænge 14</t>
+          <t xml:space="preserve">Jægervangen 12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036359</t>
+          <t xml:space="preserve">7102484</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H9">
-        <v>821</v>
+        <v>618</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,26 +571,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordrup Jagtvej 8</t>
+          <t xml:space="preserve">Jægervangen 20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2037454</t>
+          <t xml:space="preserve">7102491</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H10">
-        <v>2952</v>
+        <v>618</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,26 +631,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sognevej 39</t>
+          <t xml:space="preserve">Mosehøjvej 29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">204521, 204522</t>
+          <t xml:space="preserve">8847451</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H11">
-        <v>4044</v>
+        <v>681</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sognevej 21</t>
+          <t xml:space="preserve">Mosehøjvej 29</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">204523</t>
+          <t xml:space="preserve">8847451</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H12">
-        <v>1490</v>
+        <v>846</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,26 +751,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ermelundsvej 41</t>
+          <t xml:space="preserve">Mosehøjvej 29</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068262</t>
+          <t xml:space="preserve">8847451</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H13">
-        <v>920</v>
+        <v>401</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægersborg Alle 172</t>
+          <t xml:space="preserve">Onsgårdsvej 18</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068340</t>
+          <t xml:space="preserve">2004960</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H14">
-        <v>1536</v>
+        <v>324</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,26 +871,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brogårdsvej 85</t>
+          <t xml:space="preserve">Ordrup Jagtvej 8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069611</t>
+          <t xml:space="preserve">2037454</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H15">
-        <v>445</v>
+        <v>2952</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stolpegårdsvej 21</t>
+          <t xml:space="preserve">Sandtoften 7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,16 +941,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069718</t>
+          <t xml:space="preserve">2072808</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H16">
-        <v>870</v>
+        <v>1142</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stolpegårdsvej 25</t>
+          <t xml:space="preserve">Sandtoften 7A</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069718</t>
+          <t xml:space="preserve">2072808</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="H17">
-        <v>938</v>
+        <v>1003</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandtoften 7A</t>
+          <t xml:space="preserve">Stolpegårdsvej 21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,16 +1061,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2072808</t>
+          <t xml:space="preserve">2069718</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H18">
-        <v>1003</v>
+        <v>870</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandtoften 7</t>
+          <t xml:space="preserve">Stolpegårdsvej 25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,16 +1121,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2072808</t>
+          <t xml:space="preserve">2069718</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H19">
-        <v>1142</v>
+        <v>938</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægervangen 12</t>
+          <t xml:space="preserve">Strandvejen 144A</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">7102484</t>
+          <t xml:space="preserve">2035146</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H20">
-        <v>618</v>
+        <v>349</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,26 +1231,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægervangen 20</t>
+          <t xml:space="preserve">Tonysvej 44A</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">7102491</t>
+          <t xml:space="preserve">2006879</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>618</v>
+        <v>810</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,26 +1291,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hellerupvej 18A</t>
+          <t xml:space="preserve">Tonysvej 44A</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">8042042</t>
+          <t xml:space="preserve">2006879</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H22">
-        <v>865</v>
+        <v>375</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,40 +1351,40 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hellerupvej 18B</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 16A</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">8042042</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="H23">
-        <v>1185</v>
+        <v>1654</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200044240</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-01-12</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1411,40 +1411,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosehøjvej 29</t>
+          <t xml:space="preserve">Krøyersvej 5B</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847451</t>
+          <t xml:space="preserve">711862, 2037126</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H24">
-        <v>681</v>
+        <v>1048</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200044272</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-01-13</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1471,40 +1471,40 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosehøjvej 29</t>
+          <t xml:space="preserve">Ved Stadion 12D</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847451</t>
+          <t xml:space="preserve">8847602</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H25">
-        <v>846</v>
+        <v>489</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310024939</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-02-13</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1531,40 +1531,40 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosehøjvej 29</t>
+          <t xml:space="preserve">Ved Stadion 4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847451</t>
+          <t xml:space="preserve">711624, 8847602</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="H26">
-        <v>401</v>
+        <v>1865</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-02-13</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 16A</t>
+          <t xml:space="preserve">Ørnegårdsvej 73</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1601,25 +1601,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">8847602</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="H27">
-        <v>1654</v>
+        <v>1015</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044240</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-12</t>
+          <t xml:space="preserve">2023-02-13</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1651,35 +1651,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krøyersvej 5B</t>
+          <t xml:space="preserve">Skovshoved Havn 14A</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">711862, 2037126</t>
+          <t xml:space="preserve">711628, 2042860</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">421</t>
         </is>
       </c>
       <c r="H28">
-        <v>1048</v>
+        <v>745</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044272</t>
+          <t xml:space="preserve">311029906</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-13</t>
+          <t xml:space="preserve">2023-12-05</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1711,35 +1711,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 4</t>
+          <t xml:space="preserve">Skovshoved Havn 2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">711624, 8847602</t>
+          <t xml:space="preserve">2042860</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H29">
-        <v>1865</v>
+        <v>502</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">311029870</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-02-13</t>
+          <t xml:space="preserve">2023-12-05</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 12D</t>
+          <t xml:space="preserve">Ved Stadion 14</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="H30">
-        <v>489</v>
+        <v>11783</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">311155513</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-02-13</t>
+          <t xml:space="preserve">2026-01-26</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1831,35 +1831,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnegårdsvej 73</t>
+          <t xml:space="preserve">Gladsaxevej 4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2870</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847602</t>
+          <t xml:space="preserve">2072180</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H31">
-        <v>1015</v>
+        <v>447</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">311191661</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-02-13</t>
+          <t xml:space="preserve">2026-07-26</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovshoved Havn 2</t>
+          <t xml:space="preserve">Ordrup Jagtvej 181</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,25 +1901,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2042860</t>
+          <t xml:space="preserve">2037235</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H32">
-        <v>502</v>
+        <v>685</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311029906</t>
+          <t xml:space="preserve">311191655</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-12-05</t>
+          <t xml:space="preserve">2026-07-26</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovshoved Havn 14A</t>
+          <t xml:space="preserve">Ordrup Jagtvej 211</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,25 +1961,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">711628, 2042860</t>
+          <t xml:space="preserve">2036708</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H33">
-        <v>745</v>
+        <v>1022</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311029906</t>
+          <t xml:space="preserve">311191657</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-12-05</t>
+          <t xml:space="preserve">2026-07-26</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2011,35 +2011,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 14</t>
+          <t xml:space="preserve">Vangedevej 172</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2870</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847602</t>
+          <t xml:space="preserve">2072552</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H34">
-        <v>11783</v>
+        <v>636</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311155513</t>
+          <t xml:space="preserve">311191659</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-26</t>
+          <t xml:space="preserve">2026-07-26</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2071,17 +2071,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordrup Jagtvej 211</t>
+          <t xml:space="preserve">Vangedevej 197</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2870</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036708</t>
+          <t xml:space="preserve">2071735</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2090,11 +2090,11 @@
         </is>
       </c>
       <c r="H35">
-        <v>1022</v>
+        <v>285</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191657</t>
+          <t xml:space="preserve">311191658</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordrup Jagtvej 181</t>
+          <t xml:space="preserve">Ordrup Jagtvej 4C</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2037235</t>
+          <t xml:space="preserve">2037447</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2150,16 +2150,16 @@
         </is>
       </c>
       <c r="H36">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191655</t>
+          <t xml:space="preserve">311191957</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-26</t>
+          <t xml:space="preserve">2026-07-27</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2191,35 +2191,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vangedevej 197</t>
+          <t xml:space="preserve">Ordrup Jagtvej 6</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2870</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2071735</t>
+          <t xml:space="preserve">2037447</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H37">
-        <v>285</v>
+        <v>3140</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191658</t>
+          <t xml:space="preserve">311191957</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-26</t>
+          <t xml:space="preserve">2026-07-27</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2251,17 +2251,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gladsaxevej 4</t>
+          <t xml:space="preserve">Strandvejen 340</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2870</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2072180</t>
+          <t xml:space="preserve">2035660</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2270,16 +2270,16 @@
         </is>
       </c>
       <c r="H38">
-        <v>447</v>
+        <v>776</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191661</t>
+          <t xml:space="preserve">311191902</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-26</t>
+          <t xml:space="preserve">2026-07-27</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2311,17 +2311,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vangedevej 172</t>
+          <t xml:space="preserve">Hartmannsvej 47</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2870</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2072552</t>
+          <t xml:space="preserve">2006514</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2330,16 +2330,16 @@
         </is>
       </c>
       <c r="H39">
-        <v>636</v>
+        <v>256</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191659</t>
+          <t xml:space="preserve">311192252</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-26</t>
+          <t xml:space="preserve">2026-07-29</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2371,35 +2371,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 340</t>
+          <t xml:space="preserve">Hartmannsvej 47</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035660</t>
+          <t xml:space="preserve">2006514</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H40">
-        <v>776</v>
+        <v>325</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191902</t>
+          <t xml:space="preserve">311192252</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-27</t>
+          <t xml:space="preserve">2026-07-29</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordrup Jagtvej 4C</t>
+          <t xml:space="preserve">Hyldegårdsvej 11A</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2037447</t>
+          <t xml:space="preserve">2038903</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2450,16 +2450,16 @@
         </is>
       </c>
       <c r="H41">
-        <v>676</v>
+        <v>942</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191957</t>
+          <t xml:space="preserve">311194720</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-27</t>
+          <t xml:space="preserve">2026-08-16</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordrup Jagtvej 6</t>
+          <t xml:space="preserve">Hyldegårdsvej 18</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,25 +2501,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2037447</t>
+          <t xml:space="preserve">2038912</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H42">
-        <v>3140</v>
+        <v>1064</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311191957</t>
+          <t xml:space="preserve">311194771</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-27</t>
+          <t xml:space="preserve">2026-08-16</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hartmannsvej 47</t>
+          <t xml:space="preserve">Teglgårdsvej 5A</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006514</t>
+          <t xml:space="preserve">2036747</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2570,16 +2570,16 @@
         </is>
       </c>
       <c r="H43">
-        <v>256</v>
+        <v>413</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192252</t>
+          <t xml:space="preserve">311194703</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-29</t>
+          <t xml:space="preserve">2026-08-16</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hartmannsvej 47</t>
+          <t xml:space="preserve">Ordrup Jagtvej 112</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,25 +2621,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006514</t>
+          <t xml:space="preserve">2035105</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H44">
-        <v>325</v>
+        <v>523</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311192252</t>
+          <t xml:space="preserve">311196676</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-29</t>
+          <t xml:space="preserve">2026-08-25</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,17 +2671,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglgårdsvej 5A</t>
+          <t xml:space="preserve">Niels Andersens Vej 13A</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036747</t>
+          <t xml:space="preserve">2002351</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2690,16 +2690,16 @@
         </is>
       </c>
       <c r="H45">
-        <v>413</v>
+        <v>459</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311194703</t>
+          <t xml:space="preserve">311196855</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16</t>
+          <t xml:space="preserve">2026-08-26</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2731,35 +2731,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldegårdsvej 11A</t>
+          <t xml:space="preserve">Strandvejen 345</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2038903</t>
+          <t xml:space="preserve">8553892</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H46">
-        <v>942</v>
+        <v>708</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311194720</t>
+          <t xml:space="preserve">311197615</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16</t>
+          <t xml:space="preserve">2026-08-31</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2791,17 +2791,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldegårdsvej 18</t>
+          <t xml:space="preserve">Strandvejen 349</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2038912</t>
+          <t xml:space="preserve">8553892</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2810,16 +2810,16 @@
         </is>
       </c>
       <c r="H47">
-        <v>1064</v>
+        <v>368</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311194771</t>
+          <t xml:space="preserve">311197614</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16</t>
+          <t xml:space="preserve">2026-08-31</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2851,35 +2851,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordrup Jagtvej 112</t>
+          <t xml:space="preserve">Ved Renden 55</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2870</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035105</t>
+          <t xml:space="preserve">1300011</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H48">
-        <v>523</v>
+        <v>691</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311196676</t>
+          <t xml:space="preserve">311198202</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-25</t>
+          <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2911,45 +2911,45 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Andersens Vej 13A</t>
+          <t xml:space="preserve">Bakkevænget 12B</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002351</t>
+          <t xml:space="preserve">2070447</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H49">
-        <v>459</v>
+        <v>1806</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311196855</t>
+          <t xml:space="preserve">311199190</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-26</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2971,17 +2971,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 349</t>
+          <t xml:space="preserve">Bakkevænget 12A</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">8553892</t>
+          <t xml:space="preserve">2070447</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2990,26 +2990,26 @@
         </is>
       </c>
       <c r="H50">
-        <v>368</v>
+        <v>3927</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311197615</t>
+          <t xml:space="preserve">311199269</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3031,17 +3031,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 345</t>
+          <t xml:space="preserve">Bakkevænget 12A</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">8553892</t>
+          <t xml:space="preserve">2070447</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3050,26 +3050,26 @@
         </is>
       </c>
       <c r="H51">
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311197615</t>
+          <t xml:space="preserve">311199269</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-31</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3091,45 +3091,45 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Renden 55</t>
+          <t xml:space="preserve">Baunegårdsvej 33</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2870</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300011</t>
+          <t xml:space="preserve">8733531</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H52">
-        <v>691</v>
+        <v>737</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311198202</t>
+          <t xml:space="preserve">311199515</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-02</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevænget 12B</t>
+          <t xml:space="preserve">Skolebakken 20</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3166,20 +3166,20 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H53">
-        <v>1806</v>
+        <v>1618</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199190</t>
+          <t xml:space="preserve">311199269</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,17 +3211,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevænget 12A</t>
+          <t xml:space="preserve">Lindorffs Alle 4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070447</t>
+          <t xml:space="preserve">7904671</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="H54">
-        <v>3927</v>
+        <v>498</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199269</t>
+          <t xml:space="preserve">311201169</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-18</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,35 +3271,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevænget 12A</t>
+          <t xml:space="preserve">Margrethevej 11A</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070447</t>
+          <t xml:space="preserve">2005256</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H55">
-        <v>728</v>
+        <v>613</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199269</t>
+          <t xml:space="preserve">311201173</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-18</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 20</t>
+          <t xml:space="preserve">Nørrebakken 1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3341,25 +3341,25 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070447</t>
+          <t xml:space="preserve">2070470</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H56">
-        <v>1618</v>
+        <v>1075</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199269</t>
+          <t xml:space="preserve">311201162</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-18</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3391,35 +3391,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunegårdsvej 33</t>
+          <t xml:space="preserve">Korsgårdsvej 1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">8733531</t>
+          <t xml:space="preserve">2036778</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H57">
-        <v>737</v>
+        <v>1069</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199515</t>
+          <t xml:space="preserve">311201716</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,35 +3451,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethevej 11A</t>
+          <t xml:space="preserve">Korsgårdsvej 1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005256</t>
+          <t xml:space="preserve">2036778</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H58">
-        <v>613</v>
+        <v>1186</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201173</t>
+          <t xml:space="preserve">311201716</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-18</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,35 +3511,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebakken 1</t>
+          <t xml:space="preserve">Korsgårdsvej 1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070470</t>
+          <t xml:space="preserve">2036778</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H59">
-        <v>1075</v>
+        <v>2057</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201162</t>
+          <t xml:space="preserve">311201716</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-18</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,35 +3571,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindorffs Alle 4</t>
+          <t xml:space="preserve">Korsgårdsvej 1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">7904671</t>
+          <t xml:space="preserve">2036778</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H60">
-        <v>498</v>
+        <v>883</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201169</t>
+          <t xml:space="preserve">311201716</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-18</t>
+          <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3646,11 +3646,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H61">
-        <v>1069</v>
+        <v>5759</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3691,35 +3691,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsgårdsvej 1</t>
+          <t xml:space="preserve">Baunegårdsvej 33</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036778</t>
+          <t xml:space="preserve">8733531</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H62">
-        <v>1186</v>
+        <v>6246</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201716</t>
+          <t xml:space="preserve">311202581</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,35 +3751,35 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsgårdsvej 1</t>
+          <t xml:space="preserve">Baunegårdsvej 33</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036778</t>
+          <t xml:space="preserve">8733531</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H63">
-        <v>2057</v>
+        <v>454</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201716</t>
+          <t xml:space="preserve">311202581</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,35 +3811,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsgårdsvej 1</t>
+          <t xml:space="preserve">Baunegårdsvej 33B</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036778</t>
+          <t xml:space="preserve">8733531</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H64">
-        <v>883</v>
+        <v>644</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201716</t>
+          <t xml:space="preserve">311202581</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,35 +3871,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsgårdsvej 1</t>
+          <t xml:space="preserve">Brogårdsvej 64</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036778</t>
+          <t xml:space="preserve">2069524</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H65">
-        <v>5759</v>
+        <v>9626</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201716</t>
+          <t xml:space="preserve">311202814</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-21</t>
+          <t xml:space="preserve">2026-09-26</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunegårdsvej 33</t>
+          <t xml:space="preserve">Brogårdsvej 64</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,25 +3941,25 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">8733531</t>
+          <t xml:space="preserve">2069524</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H66">
-        <v>6246</v>
+        <v>808</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202581</t>
+          <t xml:space="preserve">311202814</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-25</t>
+          <t xml:space="preserve">2026-09-26</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunegårdsvej 33B</t>
+          <t xml:space="preserve">Brogårdsvej 64A</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4001,25 +4001,25 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">8733531</t>
+          <t xml:space="preserve">2069524</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H67">
-        <v>644</v>
+        <v>267</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202581</t>
+          <t xml:space="preserve">311202816</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-25</t>
+          <t xml:space="preserve">2026-09-26</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,35 +4051,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunegårdsvej 33</t>
+          <t xml:space="preserve">Fredensvej 35</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">8733531</t>
+          <t xml:space="preserve">8847425</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H68">
-        <v>454</v>
+        <v>744</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202581</t>
+          <t xml:space="preserve">311203109</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-25</t>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brogårdsvej 64</t>
+          <t xml:space="preserve">Grønnevænge 12</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069524</t>
+          <t xml:space="preserve">8847425</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H69">
-        <v>9626</v>
+        <v>697</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202814</t>
+          <t xml:space="preserve">311203227</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-26</t>
+          <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,35 +4171,35 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brogårdsvej 64A</t>
+          <t xml:space="preserve">Gersonsvej 38</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069524</t>
+          <t xml:space="preserve">2005606</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H70">
-        <v>267</v>
+        <v>3601</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202816</t>
+          <t xml:space="preserve">311203429</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-26</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,35 +4231,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brogårdsvej 64</t>
+          <t xml:space="preserve">Gersonsvej 38</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069524</t>
+          <t xml:space="preserve">2005606</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H71">
-        <v>808</v>
+        <v>858</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202814</t>
+          <t xml:space="preserve">311203429</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-26</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 35</t>
+          <t xml:space="preserve">Grønnevænge 14</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4306,20 +4306,20 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H72">
-        <v>744</v>
+        <v>2255</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203109</t>
+          <t xml:space="preserve">311203641</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevænge 12</t>
+          <t xml:space="preserve">Grønnevænge 16</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4366,20 +4366,20 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H73">
-        <v>697</v>
+        <v>5441</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203227</t>
+          <t xml:space="preserve">311203641</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-28</t>
+          <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,17 +4411,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gersonsvej 38</t>
+          <t xml:space="preserve">Enighedsvej 19</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005606</t>
+          <t xml:space="preserve">7102230</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4430,16 +4430,16 @@
         </is>
       </c>
       <c r="H74">
-        <v>3601</v>
+        <v>643</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203429</t>
+          <t xml:space="preserve">311278723</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-10-04</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,35 +4471,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gersonsvej 38</t>
+          <t xml:space="preserve">Bækkebo 4B</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2870</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005606</t>
+          <t xml:space="preserve">2072232</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H75">
-        <v>858</v>
+        <v>654</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203429</t>
+          <t xml:space="preserve">311204794</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevænge 16</t>
+          <t xml:space="preserve">Strandlund 148</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847425</t>
+          <t xml:space="preserve">2008702</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4550,16 +4550,16 @@
         </is>
       </c>
       <c r="H76">
-        <v>5441</v>
+        <v>307</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203641</t>
+          <t xml:space="preserve">311204805</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,35 +4591,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevænge 14</t>
+          <t xml:space="preserve">Charlottenlundvej 8A</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847425</t>
+          <t xml:space="preserve">2004165</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H77">
-        <v>2255</v>
+        <v>270</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311203641</t>
+          <t xml:space="preserve">311205140</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-29</t>
+          <t xml:space="preserve">2026-10-06</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enighedsvej 19</t>
+          <t xml:space="preserve">Charlottenlundvej 8B</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7102230</t>
+          <t xml:space="preserve">2004165</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4670,16 +4670,16 @@
         </is>
       </c>
       <c r="H78">
-        <v>643</v>
+        <v>303</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311278723</t>
+          <t xml:space="preserve">311205141</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-04</t>
+          <t xml:space="preserve">2026-10-06</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandlund 148</t>
+          <t xml:space="preserve">Dalstrøget 150</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2870</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008702</t>
+          <t xml:space="preserve">2072550</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4730,16 +4730,16 @@
         </is>
       </c>
       <c r="H79">
-        <v>307</v>
+        <v>701</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311204805</t>
+          <t xml:space="preserve">311205155</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-05</t>
+          <t xml:space="preserve">2026-10-07</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,17 +4771,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bækkebo 4B</t>
+          <t xml:space="preserve">Hartmannsvej 24</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2870</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2072232</t>
+          <t xml:space="preserve">2005774</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="H80">
-        <v>654</v>
+        <v>316</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311204794</t>
+          <t xml:space="preserve">311206074</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-05</t>
+          <t xml:space="preserve">2026-10-12</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,17 +4831,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charlottenlundvej 8B</t>
+          <t xml:space="preserve">Vangedevej 168</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2870</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004165</t>
+          <t xml:space="preserve">8159434</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="H81">
-        <v>303</v>
+        <v>479</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311205141</t>
+          <t xml:space="preserve">311206554</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-06</t>
+          <t xml:space="preserve">2026-10-13</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charlottenlundvej 8A</t>
+          <t xml:space="preserve">Hartmannsvej 22</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,25 +4901,25 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004165</t>
+          <t xml:space="preserve">2005968</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H82">
-        <v>270</v>
+        <v>4371</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311205140</t>
+          <t xml:space="preserve">311206763</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-06</t>
+          <t xml:space="preserve">2026-10-14</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,17 +4951,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalstrøget 150</t>
+          <t xml:space="preserve">Hartmannsvej 23</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2870</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2072550</t>
+          <t xml:space="preserve">2005750</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4970,16 +4970,16 @@
         </is>
       </c>
       <c r="H83">
-        <v>701</v>
+        <v>333</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311205155</t>
+          <t xml:space="preserve">311206703</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-07</t>
+          <t xml:space="preserve">2026-10-14</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hartmannsvej 24</t>
+          <t xml:space="preserve">Dæmringsvej 2</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005774</t>
+          <t xml:space="preserve">2002945</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5030,16 +5030,16 @@
         </is>
       </c>
       <c r="H84">
-        <v>316</v>
+        <v>700</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206074</t>
+          <t xml:space="preserve">311206970</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-12</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5071,17 +5071,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vangedevej 168</t>
+          <t xml:space="preserve">Hellerupvej 50</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2870</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8159434</t>
+          <t xml:space="preserve">2004758</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5090,16 +5090,16 @@
         </is>
       </c>
       <c r="H85">
-        <v>479</v>
+        <v>601</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206554</t>
+          <t xml:space="preserve">311207210</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-13</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,17 +5131,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hartmannsvej 23</t>
+          <t xml:space="preserve">Ingeborgvej 3</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005750</t>
+          <t xml:space="preserve">2006270</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5150,16 +5150,16 @@
         </is>
       </c>
       <c r="H86">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206703</t>
+          <t xml:space="preserve">311207911</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hartmannsvej 22</t>
+          <t xml:space="preserve">Gersonsvej 5</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005968</t>
+          <t xml:space="preserve">2004800</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5210,16 +5210,16 @@
         </is>
       </c>
       <c r="H87">
-        <v>4371</v>
+        <v>273</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206763</t>
+          <t xml:space="preserve">311208139</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,17 +5251,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dæmringsvej 2</t>
+          <t xml:space="preserve">L E Bruuns Vej 1B</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002945</t>
+          <t xml:space="preserve">7632032</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5270,16 +5270,16 @@
         </is>
       </c>
       <c r="H88">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311206970</t>
+          <t xml:space="preserve">311208138</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hellerupvej 50</t>
+          <t xml:space="preserve">Sankt Peders Vej 8</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004758</t>
+          <t xml:space="preserve">2018968</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5330,16 +5330,16 @@
         </is>
       </c>
       <c r="H89">
-        <v>601</v>
+        <v>485</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207210</t>
+          <t xml:space="preserve">311208140</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,17 +5371,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeborgvej 3</t>
+          <t xml:space="preserve">Tranegårdsvej 77</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006270</t>
+          <t xml:space="preserve">2008241</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="H90">
-        <v>324</v>
+        <v>409</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207911</t>
+          <t xml:space="preserve">311208141</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gersonsvej 5</t>
+          <t xml:space="preserve">Hellerupvej 5B</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,25 +5441,25 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004800</t>
+          <t xml:space="preserve">2018945</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H91">
-        <v>273</v>
+        <v>672</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208139</t>
+          <t xml:space="preserve">311208354</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,17 +5491,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tranegårdsvej 77</t>
+          <t xml:space="preserve">Springbanen 1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008241</t>
+          <t xml:space="preserve">2003860</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5510,16 +5510,16 @@
         </is>
       </c>
       <c r="H92">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208141</t>
+          <t xml:space="preserve">311208814</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,35 +5551,35 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Peders Vej 8</t>
+          <t xml:space="preserve">Springbanen 1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018968</t>
+          <t xml:space="preserve">2003860</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H93">
-        <v>485</v>
+        <v>435</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208140</t>
+          <t xml:space="preserve">311208816</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,17 +5611,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">L E Bruuns Vej 1B</t>
+          <t xml:space="preserve">Jægersborg Alle 147</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">7632032</t>
+          <t xml:space="preserve">2068313</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5630,16 +5630,16 @@
         </is>
       </c>
       <c r="H94">
-        <v>650</v>
+        <v>445</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208138</t>
+          <t xml:space="preserve">311209724</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,35 +5671,35 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hellerupvej 5B</t>
+          <t xml:space="preserve">Ejgårdsvej 18</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018945</t>
+          <t xml:space="preserve">2036359</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H95">
-        <v>672</v>
+        <v>916</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208347</t>
+          <t xml:space="preserve">311209732</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2026-11-01</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5731,17 +5731,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Springbanen 1</t>
+          <t xml:space="preserve">Lyngbyvej 270</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2003860</t>
+          <t xml:space="preserve">2002904</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5750,16 +5750,16 @@
         </is>
       </c>
       <c r="H96">
-        <v>413</v>
+        <v>769</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208814</t>
+          <t xml:space="preserve">311209896</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-11-01</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Springbanen 1</t>
+          <t xml:space="preserve">Jægervangen 37</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5801,25 +5801,25 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2003860</t>
+          <t xml:space="preserve">2068091</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H97">
-        <v>435</v>
+        <v>284</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208816</t>
+          <t xml:space="preserve">311210319</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-11-03</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægersborg Alle 147</t>
+          <t xml:space="preserve">Jægersborg Alle 139</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5861,25 +5861,25 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068313</t>
+          <t xml:space="preserve">2067876</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H98">
-        <v>445</v>
+        <v>306</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209724</t>
+          <t xml:space="preserve">311210734</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngbyvej 270</t>
+          <t xml:space="preserve">Skovvej 19</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002904</t>
+          <t xml:space="preserve">2066536</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5930,16 +5930,16 @@
         </is>
       </c>
       <c r="H99">
-        <v>769</v>
+        <v>266</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209896</t>
+          <t xml:space="preserve">311210702</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-01</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,17 +5971,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejgårdsvej 18</t>
+          <t xml:space="preserve">Smakkegårdsvej 112</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036359</t>
+          <t xml:space="preserve">2068762</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5990,16 +5990,16 @@
         </is>
       </c>
       <c r="H100">
-        <v>916</v>
+        <v>321</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209732</t>
+          <t xml:space="preserve">311210703</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-01</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægervangen 37</t>
+          <t xml:space="preserve">Jægervangen 16</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6041,25 +6041,25 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068091</t>
+          <t xml:space="preserve">7102489</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H101">
-        <v>284</v>
+        <v>636</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210350</t>
+          <t xml:space="preserve">311211003</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-03</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 19</t>
+          <t xml:space="preserve">Sauntesvej 3</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2066536</t>
+          <t xml:space="preserve">2068592</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6110,16 +6110,16 @@
         </is>
       </c>
       <c r="H102">
-        <v>266</v>
+        <v>321</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210702</t>
+          <t xml:space="preserve">311211009</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægersborg Alle 139</t>
+          <t xml:space="preserve">C L Ibsens Vej 3A</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6161,25 +6161,25 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2067876</t>
+          <t xml:space="preserve">10052046</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H103">
-        <v>306</v>
+        <v>1074</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210734</t>
+          <t xml:space="preserve">311211872</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smakkegårdsvej 112</t>
+          <t xml:space="preserve">C L Ibsens Vej 3B</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6221,25 +6221,25 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068762</t>
+          <t xml:space="preserve">10052046</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H104">
-        <v>321</v>
+        <v>600</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210703</t>
+          <t xml:space="preserve">311211872</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,17 +6271,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sauntesvej 3</t>
+          <t xml:space="preserve">Margrethevej 14</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068592</t>
+          <t xml:space="preserve">2004887</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6290,16 +6290,16 @@
         </is>
       </c>
       <c r="H105">
-        <v>321</v>
+        <v>510</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211009</t>
+          <t xml:space="preserve">311211852</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægervangen 16</t>
+          <t xml:space="preserve">Solsiden 16</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6341,25 +6341,25 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7102489</t>
+          <t xml:space="preserve">9110623</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H106">
-        <v>636</v>
+        <v>891</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211003</t>
+          <t xml:space="preserve">311211974</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-12</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">C L Ibsens Vej 3A</t>
+          <t xml:space="preserve">Skovvej 2</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">10052046</t>
+          <t xml:space="preserve">2065746</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6410,16 +6410,16 @@
         </is>
       </c>
       <c r="H107">
-        <v>1074</v>
+        <v>308</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211872</t>
+          <t xml:space="preserve">311211980</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-13</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6451,35 +6451,35 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">C L Ibsens Vej 3B</t>
+          <t xml:space="preserve">Hellerupvej 17</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">10052046</t>
+          <t xml:space="preserve">2018920</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H108">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211872</t>
+          <t xml:space="preserve">311212242</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-14</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,17 +6511,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethevej 14</t>
+          <t xml:space="preserve">Mosegårdsvej 12</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004887</t>
+          <t xml:space="preserve">2068785</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6530,16 +6530,16 @@
         </is>
       </c>
       <c r="H109">
-        <v>510</v>
+        <v>859</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211852</t>
+          <t xml:space="preserve">311214236</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solsiden 16</t>
+          <t xml:space="preserve">Mosegårdsvej 36</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">9110623</t>
+          <t xml:space="preserve">2073075</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6590,16 +6590,16 @@
         </is>
       </c>
       <c r="H110">
-        <v>891</v>
+        <v>684</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211974</t>
+          <t xml:space="preserve">311214237</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-12</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 2</t>
+          <t xml:space="preserve">Ribisvej 2</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6641,25 +6641,25 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2065746</t>
+          <t xml:space="preserve">2000399</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H111">
-        <v>308</v>
+        <v>384</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311211980</t>
+          <t xml:space="preserve">311214238</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-13</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6691,17 +6691,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hellerupvej 17</t>
+          <t xml:space="preserve">Søgårdsvej 11</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018920</t>
+          <t xml:space="preserve">2000399</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6710,16 +6710,16 @@
         </is>
       </c>
       <c r="H112">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212242</t>
+          <t xml:space="preserve">311214238</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-14</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,17 +6751,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søgårdsvej 11</t>
+          <t xml:space="preserve">Tranegårdsvej 73</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000399</t>
+          <t xml:space="preserve">2008230</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6770,11 +6770,11 @@
         </is>
       </c>
       <c r="H113">
-        <v>557</v>
+        <v>324</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214238</t>
+          <t xml:space="preserve">311214235</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ribisvej 2</t>
+          <t xml:space="preserve">Dahlensstræde 6A</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6821,25 +6821,25 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000399</t>
+          <t xml:space="preserve">2008955</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H114">
-        <v>384</v>
+        <v>520</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214238</t>
+          <t xml:space="preserve">311214489</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6871,17 +6871,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tranegårdsvej 73</t>
+          <t xml:space="preserve">Dahlensstræde 6B</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008230</t>
+          <t xml:space="preserve">2008955</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6890,16 +6890,16 @@
         </is>
       </c>
       <c r="H115">
-        <v>324</v>
+        <v>400</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214235</t>
+          <t xml:space="preserve">311214489</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosegårdsvej 12</t>
+          <t xml:space="preserve">Dahlensstræde 6C</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6941,25 +6941,25 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068785</t>
+          <t xml:space="preserve">2008955</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H116">
-        <v>859</v>
+        <v>410</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214236</t>
+          <t xml:space="preserve">311214489</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosegårdsvej 36</t>
+          <t xml:space="preserve">Dahlensstræde 6D</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7001,25 +7001,25 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2073075</t>
+          <t xml:space="preserve">2008955</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H117">
-        <v>684</v>
+        <v>424</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214237</t>
+          <t xml:space="preserve">311214489</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7051,30 +7051,30 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">L E Bruuns Vej 1A</t>
+          <t xml:space="preserve">Dahlensstræde 6E</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006242</t>
+          <t xml:space="preserve">2008955</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H118">
-        <v>300</v>
+        <v>540</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214517</t>
+          <t xml:space="preserve">311214489</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7111,30 +7111,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusvej 36</t>
+          <t xml:space="preserve">Dahlensstræde 6F</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006242</t>
+          <t xml:space="preserve">2008955</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H119">
-        <v>322</v>
+        <v>584</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214517</t>
+          <t xml:space="preserve">311214489</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusvej 36</t>
+          <t xml:space="preserve">L E Bruuns Vej 1A</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7186,11 +7186,11 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H120">
-        <v>637</v>
+        <v>300</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -7231,30 +7231,30 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dahlensstræde 6B</t>
+          <t xml:space="preserve">Rådhusvej 36</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008955</t>
+          <t xml:space="preserve">2006242</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H121">
-        <v>400</v>
+        <v>322</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214489</t>
+          <t xml:space="preserve">311214517</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7291,30 +7291,30 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dahlensstræde 6C</t>
+          <t xml:space="preserve">Rådhusvej 36</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008955</t>
+          <t xml:space="preserve">2006242</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H122">
-        <v>410</v>
+        <v>637</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214489</t>
+          <t xml:space="preserve">311214517</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dahlensstræde 6D</t>
+          <t xml:space="preserve">Ved Ungdomsboligerne 12</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7361,25 +7361,25 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008955</t>
+          <t xml:space="preserve">2069694</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H123">
-        <v>424</v>
+        <v>1920</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214489</t>
+          <t xml:space="preserve">311215775</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dahlensstræde 6E</t>
+          <t xml:space="preserve">Ved Ungdomsboligerne 22</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7421,25 +7421,25 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008955</t>
+          <t xml:space="preserve">2069694</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H124">
-        <v>540</v>
+        <v>1920</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214489</t>
+          <t xml:space="preserve">311215775</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dahlensstræde 6F</t>
+          <t xml:space="preserve">Ved Ungdomsboligerne 32</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008955</t>
+          <t xml:space="preserve">2069612</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H125">
-        <v>584</v>
+        <v>1702</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214489</t>
+          <t xml:space="preserve">311215778</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dahlensstræde 6A</t>
+          <t xml:space="preserve">Ved Ungdomsboligerne 35</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7541,25 +7541,25 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008955</t>
+          <t xml:space="preserve">2069698</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H126">
-        <v>520</v>
+        <v>1536</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311214489</t>
+          <t xml:space="preserve">311215779</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Ungdomsboligerne 32</t>
+          <t xml:space="preserve">Ved Ungdomsboligerne 42</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H127">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Ungdomsboligerne 42</t>
+          <t xml:space="preserve">Ved Ungdomsboligerne 43</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069612</t>
+          <t xml:space="preserve">2069698</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7670,11 +7670,11 @@
         </is>
       </c>
       <c r="H128">
-        <v>1702</v>
+        <v>1536</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215778</t>
+          <t xml:space="preserve">311215779</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Ungdomsboligerne 12</t>
+          <t xml:space="preserve">Lyngbyvej 431A</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069694</t>
+          <t xml:space="preserve">2069839</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="H130">
-        <v>1920</v>
+        <v>1020</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215775</t>
+          <t xml:space="preserve">311215887</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-02</t>
+          <t xml:space="preserve">2026-12-04</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Ungdomsboligerne 22</t>
+          <t xml:space="preserve">Skrænten 16</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7841,25 +7841,25 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069694</t>
+          <t xml:space="preserve">7102138</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H131">
-        <v>1920</v>
+        <v>464</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215775</t>
+          <t xml:space="preserve">311215880</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-02</t>
+          <t xml:space="preserve">2026-12-04</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Ungdomsboligerne 35</t>
+          <t xml:space="preserve">Stolpehøj 146</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069698</t>
+          <t xml:space="preserve">8286535</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -7910,16 +7910,16 @@
         </is>
       </c>
       <c r="H132">
-        <v>1536</v>
+        <v>433</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215779</t>
+          <t xml:space="preserve">311215889</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-02</t>
+          <t xml:space="preserve">2026-12-04</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Ungdomsboligerne 43</t>
+          <t xml:space="preserve">Mosebuen 3A</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7961,25 +7961,25 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069698</t>
+          <t xml:space="preserve">2069305</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H133">
-        <v>1536</v>
+        <v>580</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215779</t>
+          <t xml:space="preserve">311215975</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-02</t>
+          <t xml:space="preserve">2026-12-05</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngbyvej 431A</t>
+          <t xml:space="preserve">Stolpegårdsvej 6</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069839</t>
+          <t xml:space="preserve">2069552</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8030,16 +8030,16 @@
         </is>
       </c>
       <c r="H134">
-        <v>1020</v>
+        <v>429</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215887</t>
+          <t xml:space="preserve">311217259</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-04</t>
+          <t xml:space="preserve">2026-12-12</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skrænten 16</t>
+          <t xml:space="preserve">Stolpegårdsvej 8</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7102138</t>
+          <t xml:space="preserve">2069545</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="H135">
-        <v>464</v>
+        <v>432</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215880</t>
+          <t xml:space="preserve">311217121</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-04</t>
+          <t xml:space="preserve">2026-12-12</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stolpehøj 146</t>
+          <t xml:space="preserve">Stolpegårdsvej 12</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">8286535</t>
+          <t xml:space="preserve">2069583</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -8150,16 +8150,16 @@
         </is>
       </c>
       <c r="H136">
-        <v>433</v>
+        <v>396</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215889</t>
+          <t xml:space="preserve">311217266</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-04</t>
+          <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosebuen 3A</t>
+          <t xml:space="preserve">Vangede Bygade 45</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069305</t>
+          <t xml:space="preserve">2068782</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8210,16 +8210,16 @@
         </is>
       </c>
       <c r="H137">
-        <v>580</v>
+        <v>708</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215975</t>
+          <t xml:space="preserve">311217268</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-05</t>
+          <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stolpegårdsvej 8</t>
+          <t xml:space="preserve">Sognevej 21</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069545</t>
+          <t xml:space="preserve">204523</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8270,16 +8270,16 @@
         </is>
       </c>
       <c r="H138">
-        <v>432</v>
+        <v>1490</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217121</t>
+          <t xml:space="preserve">311217912</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-12</t>
+          <t xml:space="preserve">2026-12-15</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stolpegårdsvej 6</t>
+          <t xml:space="preserve">Sognevej 39</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8321,25 +8321,25 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069552</t>
+          <t xml:space="preserve">204521, 204522</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H139">
-        <v>429</v>
+        <v>4044</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217259</t>
+          <t xml:space="preserve">311218075</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-12</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vangede Bygade 45</t>
+          <t xml:space="preserve">Bomporten 1</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068782</t>
+          <t xml:space="preserve">2070043</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -8390,16 +8390,16 @@
         </is>
       </c>
       <c r="H140">
-        <v>708</v>
+        <v>1270</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217268</t>
+          <t xml:space="preserve">311218402</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-13</t>
+          <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stolpegårdsvej 12</t>
+          <t xml:space="preserve">Ørnegårdsvej 13</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8441,25 +8441,25 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069583</t>
+          <t xml:space="preserve">2069435</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H141">
-        <v>396</v>
+        <v>3551</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217266</t>
+          <t xml:space="preserve">311220163</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-13</t>
+          <t xml:space="preserve">2026-12-30</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bomporten 1</t>
+          <t xml:space="preserve">Ørnegårdsvej 17</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070043</t>
+          <t xml:space="preserve">2069435</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -8510,16 +8510,16 @@
         </is>
       </c>
       <c r="H142">
-        <v>1270</v>
+        <v>3524</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218402</t>
+          <t xml:space="preserve">311220163</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-18</t>
+          <t xml:space="preserve">2026-12-30</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnegårdsvej 17</t>
+          <t xml:space="preserve">Ørnegårdsvej 19</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8566,11 +8566,11 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H143">
-        <v>3524</v>
+        <v>265</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -8626,11 +8626,11 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H144">
-        <v>265</v>
+        <v>933</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnegårdsvej 13</t>
+          <t xml:space="preserve">Ørnegårdsvej 19</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8686,11 +8686,11 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H145">
-        <v>3551</v>
+        <v>716</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -8746,11 +8746,11 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H146">
-        <v>933</v>
+        <v>1269</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -8791,35 +8791,35 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnegårdsvej 19</t>
+          <t xml:space="preserve">Bernstorffsvej 161</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069435</t>
+          <t xml:space="preserve">2006876</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H147">
-        <v>716</v>
+        <v>9347</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220163</t>
+          <t xml:space="preserve">311220175</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-30</t>
+          <t xml:space="preserve">2026-12-31</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -8851,35 +8851,35 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnegårdsvej 19</t>
+          <t xml:space="preserve">Bernstorffsvej 161</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069435</t>
+          <t xml:space="preserve">2006876</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H148">
-        <v>1269</v>
+        <v>4974</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220163</t>
+          <t xml:space="preserve">311220175</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-30</t>
+          <t xml:space="preserve">2026-12-31</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8926,11 +8926,11 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H149">
-        <v>9347</v>
+        <v>1071</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -9031,35 +9031,35 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernstorffsvej 161</t>
+          <t xml:space="preserve">Ahlmanns Alle 6</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006876</t>
+          <t xml:space="preserve">2005642</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H151">
-        <v>4974</v>
+        <v>4984</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220175</t>
+          <t xml:space="preserve">311232130</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-31</t>
+          <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernstorffsvej 161</t>
+          <t xml:space="preserve">Bernstorffsvej 159</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9101,25 +9101,25 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006876</t>
+          <t xml:space="preserve">2006712</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H152">
-        <v>1071</v>
+        <v>3975</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220175</t>
+          <t xml:space="preserve">311232713</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-31</t>
+          <t xml:space="preserve">2027-03-08</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9151,35 +9151,35 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahlmanns Alle 6</t>
+          <t xml:space="preserve">Bernstorffsvej 159</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005642</t>
+          <t xml:space="preserve">2006712</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H153">
-        <v>4984</v>
+        <v>727</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311232130</t>
+          <t xml:space="preserve">311232714</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-05</t>
+          <t xml:space="preserve">2027-03-08</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9211,35 +9211,35 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernstorffsvej 159</t>
+          <t xml:space="preserve">C L Ibsens Vej 3</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006712</t>
+          <t xml:space="preserve">10052046</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H154">
-        <v>3975</v>
+        <v>1404</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311232713</t>
+          <t xml:space="preserve">311236053</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-08</t>
+          <t xml:space="preserve">2027-03-23</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9271,35 +9271,35 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernstorffsvej 159</t>
+          <t xml:space="preserve">Dessaus Boulevard 10</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006712</t>
+          <t xml:space="preserve">8917277</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H155">
-        <v>727</v>
+        <v>8434</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311232714</t>
+          <t xml:space="preserve">311236293</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-08</t>
+          <t xml:space="preserve">2027-03-23</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9331,35 +9331,35 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">C L Ibsens Vej 3</t>
+          <t xml:space="preserve">Bregnegårdsvej 17</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">10052046</t>
+          <t xml:space="preserve">9305089</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H156">
-        <v>1404</v>
+        <v>2193</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236053</t>
+          <t xml:space="preserve">311236656</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-23</t>
+          <t xml:space="preserve">2027-03-25</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9391,17 +9391,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dessaus Boulevard 10</t>
+          <t xml:space="preserve">Kirkevej 7A</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">8917277</t>
+          <t xml:space="preserve">2038916</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -9410,16 +9410,16 @@
         </is>
       </c>
       <c r="H157">
-        <v>8434</v>
+        <v>706</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236293</t>
+          <t xml:space="preserve">311237048</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-23</t>
+          <t xml:space="preserve">2027-03-27</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9451,35 +9451,35 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bregnegårdsvej 17</t>
+          <t xml:space="preserve">Bernstorffsvej 155</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305089</t>
+          <t xml:space="preserve">2006875</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H158">
-        <v>2193</v>
+        <v>1635</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236656</t>
+          <t xml:space="preserve">311242890</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-25</t>
+          <t xml:space="preserve">2027-04-25</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -9511,17 +9511,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 7A</t>
+          <t xml:space="preserve">Maglegård Skolevej 1</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2038916</t>
+          <t xml:space="preserve">9305089</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -9530,16 +9530,16 @@
         </is>
       </c>
       <c r="H159">
-        <v>706</v>
+        <v>1149</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311237048</t>
+          <t xml:space="preserve">311243583</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-27</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9571,35 +9571,35 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernstorffsvej 155</t>
+          <t xml:space="preserve">Maglegård Skolevej 1A</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006875</t>
+          <t xml:space="preserve">9305089</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H160">
-        <v>1635</v>
+        <v>701</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311242890</t>
+          <t xml:space="preserve">311243583</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-25</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -9631,30 +9631,30 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Renden 57</t>
+          <t xml:space="preserve">Maglegård Skolevej 1C</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2870</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300011</t>
+          <t xml:space="preserve">9305089</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H161">
-        <v>400</v>
+        <v>2692</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243628</t>
+          <t xml:space="preserve">311243583</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenagervej 1</t>
+          <t xml:space="preserve">Maglegård Skolevej 1C</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9701,20 +9701,20 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2001527</t>
+          <t xml:space="preserve">9305089</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H162">
-        <v>759</v>
+        <v>536</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243656</t>
+          <t xml:space="preserve">311243583</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maglegård Skolevej 1</t>
+          <t xml:space="preserve">Maglegård Skolevej 1D</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9766,11 +9766,11 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H163">
-        <v>1149</v>
+        <v>709</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maglegård Skolevej 1D</t>
+          <t xml:space="preserve">Stenagervej 1</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9821,20 +9821,20 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305089</t>
+          <t xml:space="preserve">2001527</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H164">
-        <v>709</v>
+        <v>759</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243583</t>
+          <t xml:space="preserve">311243656</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9871,30 +9871,30 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maglegård Skolevej 1A</t>
+          <t xml:space="preserve">Ved Renden 57</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2870</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305089</t>
+          <t xml:space="preserve">1300011</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H165">
-        <v>701</v>
+        <v>400</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243583</t>
+          <t xml:space="preserve">311243628</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maglegård Skolevej 1C</t>
+          <t xml:space="preserve">Dyssegårdsvej 24</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9941,25 +9941,25 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305089</t>
+          <t xml:space="preserve">2001352</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H166">
-        <v>2692</v>
+        <v>517</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243583</t>
+          <t xml:space="preserve">311244012</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-04-28</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maglegård Skolevej 1C</t>
+          <t xml:space="preserve">Dyssegårdsvej 26</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10001,25 +10001,25 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305089</t>
+          <t xml:space="preserve">2001352</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H167">
-        <v>536</v>
+        <v>5437</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311243583</t>
+          <t xml:space="preserve">311244012</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-04-28</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyssegårdsvej 26</t>
+          <t xml:space="preserve">Dyssegårdsvej 26B</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10066,11 +10066,11 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H168">
-        <v>5437</v>
+        <v>785</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -10111,35 +10111,35 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyssegårdsvej 26B</t>
+          <t xml:space="preserve">Mariebjergvej 1</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2001352</t>
+          <t xml:space="preserve">2069384</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H169">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311244012</t>
+          <t xml:space="preserve">311245806</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-28</t>
+          <t xml:space="preserve">2027-05-07</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyssegårdsvej 24</t>
+          <t xml:space="preserve">Bregnegårdsvej 21B</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10181,25 +10181,25 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2001352</t>
+          <t xml:space="preserve">9305092</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H170">
-        <v>517</v>
+        <v>1579</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311244012</t>
+          <t xml:space="preserve">311246144</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-28</t>
+          <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -10231,35 +10231,35 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mariebjergvej 1</t>
+          <t xml:space="preserve">Bregnegårdsvej 21B</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069384</t>
+          <t xml:space="preserve">9305092</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H171">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311245806</t>
+          <t xml:space="preserve">311246144</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-07</t>
+          <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">C V E Knuths Vej 1</t>
+          <t xml:space="preserve">Bregnegårdsvej 21B</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10301,20 +10301,20 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002588</t>
+          <t xml:space="preserve">9305092</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H172">
-        <v>750</v>
+        <v>362</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246147</t>
+          <t xml:space="preserve">311246144</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hellerupvej 18</t>
+          <t xml:space="preserve">Bregnegårdsvej 21B</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10361,20 +10361,20 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004925</t>
+          <t xml:space="preserve">9305092</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H173">
-        <v>546</v>
+        <v>256</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246229</t>
+          <t xml:space="preserve">311246144</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10471,17 +10471,17 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Schioldannsvej 31</t>
+          <t xml:space="preserve">C V E Knuths Vej 1</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2038849</t>
+          <t xml:space="preserve">2002588</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -10490,11 +10490,11 @@
         </is>
       </c>
       <c r="H175">
-        <v>5742</v>
+        <v>750</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246445</t>
+          <t xml:space="preserve">311246147</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10531,30 +10531,30 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldegårds Tværvej 12</t>
+          <t xml:space="preserve">Hellerupvej 18</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2038849</t>
+          <t xml:space="preserve">2004925</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H176">
-        <v>3226</v>
+        <v>546</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246446</t>
+          <t xml:space="preserve">311246229</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10591,30 +10591,30 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bregnegårdsvej 21B</t>
+          <t xml:space="preserve">Hyldegårds Tværvej 12</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305092</t>
+          <t xml:space="preserve">2038849</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H177">
-        <v>1579</v>
+        <v>3226</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246144</t>
+          <t xml:space="preserve">311246446</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10651,30 +10651,30 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bregnegårdsvej 21B</t>
+          <t xml:space="preserve">Schioldannsvej 31</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305092</t>
+          <t xml:space="preserve">2038849</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H178">
-        <v>783</v>
+        <v>5742</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246144</t>
+          <t xml:space="preserve">311246445</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10711,35 +10711,35 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bregnegårdsvej 21B</t>
+          <t xml:space="preserve">C L Ibsens Vej 60</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305092</t>
+          <t xml:space="preserve">2069531</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H179">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246144</t>
+          <t xml:space="preserve">311246563</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-09</t>
+          <t xml:space="preserve">2027-05-10</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -10771,35 +10771,35 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bregnegårdsvej 21B</t>
+          <t xml:space="preserve">Søndersøvej 41A</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305092</t>
+          <t xml:space="preserve">199954</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H180">
-        <v>256</v>
+        <v>5288</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246144</t>
+          <t xml:space="preserve">311246755</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-09</t>
+          <t xml:space="preserve">2027-05-10</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -10831,17 +10831,17 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">C L Ibsens Vej 60</t>
+          <t xml:space="preserve">Bregnegårdsvej 28B</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069531</t>
+          <t xml:space="preserve">2006002</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10850,16 +10850,16 @@
         </is>
       </c>
       <c r="H181">
-        <v>373</v>
+        <v>702</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246563</t>
+          <t xml:space="preserve">311246796</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-10</t>
+          <t xml:space="preserve">2027-05-11</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -10891,17 +10891,17 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bregnegårdsvej 28B</t>
+          <t xml:space="preserve">Bakkevænget 17</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006002</t>
+          <t xml:space="preserve">8067646</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -10910,16 +10910,16 @@
         </is>
       </c>
       <c r="H182">
-        <v>702</v>
+        <v>750</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246796</t>
+          <t xml:space="preserve">311248917</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-11</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -11011,35 +11011,35 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevænget 17</t>
+          <t xml:space="preserve">Bregnegårdsvej 21A</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">8067646</t>
+          <t xml:space="preserve">9305092</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H184">
-        <v>750</v>
+        <v>831</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248917</t>
+          <t xml:space="preserve">311249281</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -11131,35 +11131,35 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bregnegårdsvej 21A</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 11</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305092</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H186">
-        <v>831</v>
+        <v>373</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311249281</t>
+          <t xml:space="preserve">311251574</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-23</t>
+          <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 2A</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 17</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11206,11 +11206,11 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H187">
-        <v>287</v>
+        <v>389</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 2B</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 2A</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11266,11 +11266,11 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H188">
-        <v>373</v>
+        <v>287</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 3</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 2B</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H189">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 5</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 3</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H190">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 11</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 5</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H191">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 17</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 1</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11506,20 +11506,20 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H192">
-        <v>389</v>
+        <v>1119</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251574</t>
+          <t xml:space="preserve">311251715</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-02</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 1</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 13</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11566,11 +11566,11 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H193">
-        <v>1119</v>
+        <v>405</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 4</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 15</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11626,11 +11626,11 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H194">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 6</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 4</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H195">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 7</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 6</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11746,11 +11746,11 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H196">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 9</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 7</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11806,11 +11806,11 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H197">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 13</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 9</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -11866,11 +11866,11 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H198">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -11911,35 +11911,35 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 15</t>
+          <t xml:space="preserve">Niels Andersens Vej 6</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">2002621</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H199">
-        <v>405</v>
+        <v>12354</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251715</t>
+          <t xml:space="preserve">311252789</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2027-06-09</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -11971,35 +11971,35 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Andersens Vej 6</t>
+          <t xml:space="preserve">Nybrovej 35</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002621</t>
+          <t xml:space="preserve">2069701</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H200">
-        <v>12354</v>
+        <v>980</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311252789</t>
+          <t xml:space="preserve">311295881</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-09</t>
+          <t xml:space="preserve">2028-02-02</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -12151,35 +12151,35 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 35</t>
+          <t xml:space="preserve">Hellerupvej 20</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069701</t>
+          <t xml:space="preserve">8042042</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H203">
-        <v>980</v>
+        <v>1297</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295881</t>
+          <t xml:space="preserve">311298255</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-02</t>
+          <t xml:space="preserve">2028-02-17</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hellerupvej 20</t>
+          <t xml:space="preserve">Hellerupvej 22</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -12286,15 +12286,15 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H205">
-        <v>1297</v>
+        <v>1534</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298255</t>
+          <t xml:space="preserve">311298256</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -12331,17 +12331,17 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hellerupvej 22</t>
+          <t xml:space="preserve">Skovgårdsvej 56B</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">8042042</t>
+          <t xml:space="preserve">1300936</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -12350,16 +12350,16 @@
         </is>
       </c>
       <c r="H206">
-        <v>1534</v>
+        <v>966</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298256</t>
+          <t xml:space="preserve">311302882</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-17</t>
+          <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -12391,35 +12391,35 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovgårdsvej 56B</t>
+          <t xml:space="preserve">Mosebuen 28B</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300936</t>
+          <t xml:space="preserve">8847600</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H207">
-        <v>966</v>
+        <v>1170</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311302882</t>
+          <t xml:space="preserve">311303245</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-15</t>
+          <t xml:space="preserve">2028-03-16</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -12451,17 +12451,17 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosebuen 28B</t>
+          <t xml:space="preserve">Morescosvej 11A</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847600</t>
+          <t xml:space="preserve">2036431</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -12470,16 +12470,16 @@
         </is>
       </c>
       <c r="H208">
-        <v>1170</v>
+        <v>895</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311303245</t>
+          <t xml:space="preserve">311303980</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-16</t>
+          <t xml:space="preserve">2028-03-20</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morescosvej 11A</t>
+          <t xml:space="preserve">Teglgårdsvej 11A</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036431</t>
+          <t xml:space="preserve">2036994</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -12530,16 +12530,16 @@
         </is>
       </c>
       <c r="H209">
-        <v>895</v>
+        <v>263</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311303980</t>
+          <t xml:space="preserve">311304249</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-20</t>
+          <t xml:space="preserve">2028-03-21</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -12566,22 +12566,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t xml:space="preserve">157</t>
+          <t xml:space="preserve">210</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglgårdsvej 11A</t>
+          <t xml:space="preserve">Rødehusvej 2</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2990</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036994</t>
+          <t xml:space="preserve">9156756</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -12590,16 +12590,16 @@
         </is>
       </c>
       <c r="H210">
-        <v>263</v>
+        <v>3840</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311304249</t>
+          <t xml:space="preserve">311306645</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-21</t>
+          <t xml:space="preserve">2028-04-05</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -12626,40 +12626,40 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t xml:space="preserve">210</t>
+          <t xml:space="preserve">157</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødehusvej 2</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 14A</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">9156756</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="H211">
-        <v>3840</v>
+        <v>2455</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306649</t>
+          <t xml:space="preserve">311387113</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-05</t>
+          <t xml:space="preserve">2029-07-05</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 14A</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 10A</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -12706,20 +12706,20 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="H212">
-        <v>2455</v>
+        <v>2051</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311387113</t>
+          <t xml:space="preserve">311584848</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-05</t>
+          <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 8A</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 12</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12766,15 +12766,15 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="H213">
-        <v>2046</v>
+        <v>572</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584847</t>
+          <t xml:space="preserve">311391980</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 10A</t>
+          <t xml:space="preserve">Bank-Mikkelsens Vej 8A</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -12826,15 +12826,15 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="H214">
-        <v>2051</v>
+        <v>2046</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584848</t>
+          <t xml:space="preserve">311584847</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank-Mikkelsens Vej 12</t>
+          <t xml:space="preserve">Adolphsvej 25</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -12881,25 +12881,25 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">2000002</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H215">
-        <v>572</v>
+        <v>1405</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311391980</t>
+          <t xml:space="preserve">311461983</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-08</t>
+          <t xml:space="preserve">2030-09-18</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adolphsvej 25</t>
+          <t xml:space="preserve">Stolpehøj 148</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12941,25 +12941,25 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000002</t>
+          <t xml:space="preserve">2070356</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H216">
-        <v>1405</v>
+        <v>3922</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311461983</t>
+          <t xml:space="preserve">311515578</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-18</t>
+          <t xml:space="preserve">2031-04-26</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stolpehøj 148</t>
+          <t xml:space="preserve">Stolpehøj 148A</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -13006,11 +13006,11 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H217">
-        <v>3922</v>
+        <v>1281</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stolpehøj 148A</t>
+          <t xml:space="preserve">Stolpehøj 148C</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -13066,20 +13066,20 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H218">
-        <v>1281</v>
+        <v>636</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311515578</t>
+          <t xml:space="preserve">311526742</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-26</t>
+          <t xml:space="preserve">2031-06-09</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stolpehøj 148C</t>
+          <t xml:space="preserve">Jægervangen 39</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -13121,25 +13121,25 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070356</t>
+          <t xml:space="preserve">2068210</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H219">
-        <v>636</v>
+        <v>566</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526742</t>
+          <t xml:space="preserve">311552980</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-09</t>
+          <t xml:space="preserve">2031-10-05</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægervangen 39</t>
+          <t xml:space="preserve">Ermelundsvej 41</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068210</t>
+          <t xml:space="preserve">2068262</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -13190,16 +13190,16 @@
         </is>
       </c>
       <c r="H220">
-        <v>566</v>
+        <v>506</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552980</t>
+          <t xml:space="preserve">311556816</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-05</t>
+          <t xml:space="preserve">2031-10-21</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ermelundsvej 41</t>
+          <t xml:space="preserve">Ermelundsvej 58A</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -13241,20 +13241,20 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068262</t>
+          <t xml:space="preserve">2068330</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H221">
-        <v>506</v>
+        <v>580</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556816</t>
+          <t xml:space="preserve">311556838</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægersborg Alle 143A</t>
+          <t xml:space="preserve">Ermelundsvej 60</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -13306,11 +13306,11 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H222">
-        <v>388</v>
+        <v>302</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægersborg Alle 145A</t>
+          <t xml:space="preserve">Jægersborg Alle 143A</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -13366,11 +13366,11 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H223">
-        <v>290</v>
+        <v>388</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ermelundsvej 58A</t>
+          <t xml:space="preserve">Jægersborg Alle 145A</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -13426,11 +13426,11 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H224">
-        <v>580</v>
+        <v>290</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ermelundsvej 60</t>
+          <t xml:space="preserve">Stolpegårdsvej 14A</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -13481,25 +13481,25 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2068330</t>
+          <t xml:space="preserve">2069534</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H225">
-        <v>302</v>
+        <v>2580</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311556838</t>
+          <t xml:space="preserve">311559143</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-21</t>
+          <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stolpegårdsvej 14A</t>
+          <t xml:space="preserve">Stolpegårdsvej 29</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -13541,20 +13541,20 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069534</t>
+          <t xml:space="preserve">2069714</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H226">
-        <v>2580</v>
+        <v>870</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559143</t>
+          <t xml:space="preserve">311559292</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stolpegårdsvej 29</t>
+          <t xml:space="preserve">Stolpegårdsvej 33</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H227">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stolpegårdsvej 33</t>
+          <t xml:space="preserve">Stolpegårdsvej 37</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -13666,11 +13666,11 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H228">
-        <v>870</v>
+        <v>888</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
@@ -13711,35 +13711,35 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stolpegårdsvej 37</t>
+          <t xml:space="preserve">Skovgårdsvej 56</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069714</t>
+          <t xml:space="preserve">1300936</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H229">
-        <v>888</v>
+        <v>4249</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559292</t>
+          <t xml:space="preserve">311565422</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-02</t>
+          <t xml:space="preserve">2031-12-01</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -13771,7 +13771,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovgårdsvej 56</t>
+          <t xml:space="preserve">Skovgårdsvej 56A</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -13786,15 +13786,15 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H230">
-        <v>4249</v>
+        <v>306</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311565422</t>
+          <t xml:space="preserve">311565462</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -13831,35 +13831,35 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovgårdsvej 56A</t>
+          <t xml:space="preserve">Skolevej 36</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300936</t>
+          <t xml:space="preserve">2003344</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H231">
-        <v>306</v>
+        <v>1755</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311565462</t>
+          <t xml:space="preserve">311568018</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-01</t>
+          <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -13891,17 +13891,17 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 36</t>
+          <t xml:space="preserve">Ejgårdsvej 11</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2003344</t>
+          <t xml:space="preserve">2036292</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -13910,16 +13910,16 @@
         </is>
       </c>
       <c r="H232">
-        <v>1755</v>
+        <v>3539</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568018</t>
+          <t xml:space="preserve">311569171</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -13951,17 +13951,17 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejgårdsvej 11</t>
+          <t xml:space="preserve">Krøyersvej 5A</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036292</t>
+          <t xml:space="preserve">2037126</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -13970,11 +13970,11 @@
         </is>
       </c>
       <c r="H233">
-        <v>3539</v>
+        <v>2236</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569171</t>
+          <t xml:space="preserve">311569166</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -14026,11 +14026,11 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H234">
-        <v>2236</v>
+        <v>913</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
@@ -14086,11 +14086,11 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H235">
-        <v>913</v>
+        <v>1810</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
@@ -14146,11 +14146,11 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H236">
-        <v>1810</v>
+        <v>820</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
@@ -14191,35 +14191,35 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krøyersvej 5A</t>
+          <t xml:space="preserve">Stolpehøj 150</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2037126</t>
+          <t xml:space="preserve">2070356</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H237">
-        <v>820</v>
+        <v>1717</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569166</t>
+          <t xml:space="preserve">311569804</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-21</t>
+          <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandparksvej 42</t>
+          <t xml:space="preserve">Strandparksvej 36A</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -14266,11 +14266,11 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H238">
-        <v>394</v>
+        <v>335</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -14326,11 +14326,11 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H239">
-        <v>335</v>
+        <v>307</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -14386,11 +14386,11 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H240">
-        <v>307</v>
+        <v>1479</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandparksvej 36A</t>
+          <t xml:space="preserve">Strandparksvej 42</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -14446,11 +14446,11 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H241">
-        <v>1479</v>
+        <v>394</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
@@ -14491,35 +14491,35 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stolpehøj 150</t>
+          <t xml:space="preserve">Paul Elvstrøms Plads 1</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2070356</t>
+          <t xml:space="preserve">2005056</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H242">
-        <v>1717</v>
+        <v>927</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569804</t>
+          <t xml:space="preserve">311570312</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-23</t>
+          <t xml:space="preserve">2032-01-03</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -14551,35 +14551,35 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paul Elvstrøms Plads 1</t>
+          <t xml:space="preserve">C L Ibsens Vej 70</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005056</t>
+          <t xml:space="preserve">8847602</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="H243">
-        <v>927</v>
+        <v>650</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570312</t>
+          <t xml:space="preserve">311574868</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-03</t>
+          <t xml:space="preserve">2032-01-26</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">C L Ibsens Vej 70</t>
+          <t xml:space="preserve">Ved Stadion 6</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14626,11 +14626,11 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H244">
-        <v>650</v>
+        <v>4863</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 6</t>
+          <t xml:space="preserve">Ved Stadion 10</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -14686,20 +14686,20 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H245">
-        <v>4863</v>
+        <v>1010</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574868</t>
+          <t xml:space="preserve">311575200</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-26</t>
+          <t xml:space="preserve">2032-01-27</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 10</t>
+          <t xml:space="preserve">Palle Simonsens Vej 21A</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14741,25 +14741,25 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847602</t>
+          <t xml:space="preserve">2069741</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">89</t>
         </is>
       </c>
       <c r="H246">
-        <v>1010</v>
+        <v>2051</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575200</t>
+          <t xml:space="preserve">311584797</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-27</t>
+          <t xml:space="preserve">2032-03-14</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palle Simonsens Vej 21A</t>
+          <t xml:space="preserve">Palle Simonsens Vej 23A</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -14806,15 +14806,15 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">89</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
       <c r="H247">
-        <v>2051</v>
+        <v>2046</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584797</t>
+          <t xml:space="preserve">311584799</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -14851,7 +14851,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Palle Simonsens Vej 23A</t>
+          <t xml:space="preserve">Sognevej 40A</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -14866,15 +14866,15 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">91</t>
         </is>
       </c>
       <c r="H248">
-        <v>2046</v>
+        <v>2051</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584799</t>
+          <t xml:space="preserve">311584803</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -14911,35 +14911,35 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sognevej 40A</t>
+          <t xml:space="preserve">Korsgårdsvej 5</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069741</t>
+          <t xml:space="preserve">2037271</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">91</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H249">
-        <v>2051</v>
+        <v>1161</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311584803</t>
+          <t xml:space="preserve">311590761</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-14</t>
+          <t xml:space="preserve">2032-04-05</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -14971,35 +14971,35 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsgårdsvej 5</t>
+          <t xml:space="preserve">Jægersborg Alle 148C</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2037271</t>
+          <t xml:space="preserve">2067880</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H250">
-        <v>1161</v>
+        <v>6480</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590761</t>
+          <t xml:space="preserve">311598275</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-05</t>
+          <t xml:space="preserve">2032-05-06</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægersborg Alle 148C</t>
+          <t xml:space="preserve">Ved Stadion 8</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -15041,25 +15041,25 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2067880</t>
+          <t xml:space="preserve">8847602</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H251">
-        <v>6480</v>
+        <v>3780</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598275</t>
+          <t xml:space="preserve">311603147</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-06</t>
+          <t xml:space="preserve">2032-05-25</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -15091,35 +15091,35 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Stadion 8</t>
+          <t xml:space="preserve">Skovshoved Havn 16B</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847602</t>
+          <t xml:space="preserve">2042860</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="H252">
-        <v>3780</v>
+        <v>575</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311603147</t>
+          <t xml:space="preserve">311679358</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-25</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -15151,35 +15151,35 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovshoved Havn 16B</t>
+          <t xml:space="preserve">Duntzfelts Alle 8</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2042860</t>
+          <t xml:space="preserve">2005284</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H253">
-        <v>575</v>
+        <v>1582</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679358</t>
+          <t xml:space="preserve">311712629</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2033-10-05</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -15211,17 +15211,17 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duntzfelts Alle 8</t>
+          <t xml:space="preserve">Jægersborg Alle 139</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005284</t>
+          <t xml:space="preserve">2067876</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -15230,11 +15230,11 @@
         </is>
       </c>
       <c r="H254">
-        <v>1582</v>
+        <v>735</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712629</t>
+          <t xml:space="preserve">311712640</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -15271,17 +15271,17 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægersborg Alle 139</t>
+          <t xml:space="preserve">Ordrup Vænge 122</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2067876</t>
+          <t xml:space="preserve">197867, 197868</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -15290,16 +15290,16 @@
         </is>
       </c>
       <c r="H255">
-        <v>735</v>
+        <v>922</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712640</t>
+          <t xml:space="preserve">311716715</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-05</t>
+          <t xml:space="preserve">2033-10-23</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -15331,30 +15331,30 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skelvej 1</t>
+          <t xml:space="preserve">Ordrup Vænge 102</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002329</t>
+          <t xml:space="preserve">2039786</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H256">
-        <v>425</v>
+        <v>350</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717184</t>
+          <t xml:space="preserve">311717187</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordrup Vænge 28</t>
+          <t xml:space="preserve">Ordrup Vænge 124</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -15406,11 +15406,11 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H257">
-        <v>350</v>
+        <v>315</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordrup Vænge 84</t>
+          <t xml:space="preserve">Ordrup Vænge 28</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -15466,11 +15466,11 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H258">
-        <v>315</v>
+        <v>350</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordrup Vænge 102</t>
+          <t xml:space="preserve">Ordrup Vænge 84</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -15526,11 +15526,11 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H259">
-        <v>350</v>
+        <v>315</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
@@ -15571,30 +15571,30 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ordrup Vænge 124</t>
+          <t xml:space="preserve">Skelvej 1</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2900</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2039786</t>
+          <t xml:space="preserve">2002329</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H260">
-        <v>315</v>
+        <v>425</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717187</t>
+          <t xml:space="preserve">311717184</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -15931,17 +15931,17 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnestien 11</t>
+          <t xml:space="preserve">Broholms Alle 19A</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2820</t>
+          <t xml:space="preserve">2920</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2069441</t>
+          <t xml:space="preserve">8847469</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -15950,11 +15950,11 @@
         </is>
       </c>
       <c r="H266">
-        <v>720</v>
+        <v>1231</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800431</t>
+          <t xml:space="preserve">311800430</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -15991,7 +15991,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Broholms Alle 19A</t>
+          <t xml:space="preserve">Broholms Alle 25</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -16006,11 +16006,11 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H267">
-        <v>1231</v>
+        <v>2040</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
@@ -16051,30 +16051,30 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Broholms Alle 25</t>
+          <t xml:space="preserve">Tjørnestien 11</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920</t>
+          <t xml:space="preserve">2820</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">8847469</t>
+          <t xml:space="preserve">2069441</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H268">
-        <v>2040</v>
+        <v>720</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800430</t>
+          <t xml:space="preserve">311800431</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">

--- a/public/exports/19438414.xlsx
+++ b/public/exports/19438414.xlsx
@@ -1554,7 +1554,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">

--- a/public/exports/19438414.xlsx
+++ b/public/exports/19438414.xlsx
@@ -1494,7 +1494,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024939</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311029870</t>
+          <t xml:space="preserve">311029906</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210319</t>
+          <t xml:space="preserve">311210350</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295879</t>
+          <t xml:space="preserve">311295882</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">

--- a/public/exports/19438414.xlsx
+++ b/public/exports/19438414.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L272"/>
+  <dimension ref="A1:M272"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-01-12</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kuben Management A/S</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-01-13</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1494,20 +1614,25 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-02-13</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1554,20 +1679,25 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-02-13</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1614,20 +1744,25 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024938</t>
+          <t xml:space="preserve">310024942</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-02-13</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-12-05</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-12-05</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-26</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-07-26</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-07-26</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-07-26</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-07-26</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-07-26</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-07-27</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-07-27</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-07-27</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-07-29</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-07-29</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-16</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-16</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-16</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-25</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-26</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-31</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2814,20 +3044,25 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311197614</t>
+          <t xml:space="preserve">311197615</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-31</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-02</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-18</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-18</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-18</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-26</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-26</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-26</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-29</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-04</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-06</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-06</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-07</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-12</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-13</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-14</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-14</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5454,20 +5904,25 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208354</t>
+          <t xml:space="preserve">311208347</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-01</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-01</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5814,20 +6294,25 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210350</t>
+          <t xml:space="preserve">311210319</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-03</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-12</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-13</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-14</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-02</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-04</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-04</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-04</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-05</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-12</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-12</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-13</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-15</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-30</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-30</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-30</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-30</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-30</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-30</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-31</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-31</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-31</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-31</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-08</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-08</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-23</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-23</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-25</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-27</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-25</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-28</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-28</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-28</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-07</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-09</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-10</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-10</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-11</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-09</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-02</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-02</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12114,20 +13119,25 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295882</t>
+          <t xml:space="preserve">311295879</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-02</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-17</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-17</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-17</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-15</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-16</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-20</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-03-21</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12594,20 +13639,25 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306645</t>
+          <t xml:space="preserve">311306649</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-04-05</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">LKH Rådgivning</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-07-05</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">LKH Rådgivning</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">LKH Rådgivning</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">LKH Rådgivning</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-08</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-18</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-26</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-04-26</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-09</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-05</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-21</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-21</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-21</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,15 +14489,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-21</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13439,15 +14554,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-10-21</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13499,15 +14619,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13559,15 +14684,20 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13619,15 +14749,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13679,15 +14814,20 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-02</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13739,15 +14879,20 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-01</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13799,15 +14944,20 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-01</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13859,15 +15009,20 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13919,15 +15074,20 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13979,15 +15139,20 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14039,15 +15204,20 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14099,15 +15269,20 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14159,15 +15334,20 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14219,15 +15399,20 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14279,15 +15464,20 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14339,15 +15529,20 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14399,15 +15594,20 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14459,15 +15659,20 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-23</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14519,15 +15724,20 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-03</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14579,15 +15789,20 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-26</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14639,15 +15854,20 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-26</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14699,15 +15919,20 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-27</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14759,15 +15984,20 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
+          <t xml:space="preserve">LKH Rådgivning</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-14</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14819,15 +16049,20 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
+          <t xml:space="preserve">LKH Rådgivning</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-14</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14879,15 +16114,20 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
+          <t xml:space="preserve">LKH Rådgivning</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-14</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14939,15 +16179,20 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
+          <t xml:space="preserve">MOE A/S</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-05</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14999,15 +16244,20 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
+          <t xml:space="preserve">B.F. Byggeservice ApS</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-06</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15059,15 +16309,20 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
+          <t xml:space="preserve">HJ-Energi ApS</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-25</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15119,15 +16374,20 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15179,15 +16439,20 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fried-Energi ApS</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-05</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15239,15 +16504,20 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fried-Energi ApS</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-05</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15299,15 +16569,20 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fried-Energi ApS</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-23</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15359,15 +16634,20 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fried-Energi ApS</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-24</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15419,15 +16699,20 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fried-Energi ApS</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-24</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15479,15 +16764,20 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fried-Energi ApS</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-24</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15539,15 +16829,20 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fried-Energi ApS</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-24</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15599,15 +16894,20 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fried-Energi ApS</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-24</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15659,15 +16959,20 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fried-Energi ApS</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15719,15 +17024,20 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fried-Energi ApS</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-02</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15779,15 +17089,20 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fried-Energi ApS</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-04</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15839,15 +17154,20 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fried-Energi ApS</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-04</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15899,15 +17219,20 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fried-Energi ApS</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-06</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15959,15 +17284,20 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-02</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16019,15 +17349,20 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-02</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16079,15 +17414,20 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-02</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16139,15 +17479,20 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-10</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16199,15 +17544,20 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-17</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16259,15 +17609,20 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-23</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16319,21 +17674,26 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-01-16</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L272" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L272"/>
+  <autoFilter ref="A1:M272"/>
 </worksheet>
 </file>
--- a/public/exports/19438414.xlsx
+++ b/public/exports/19438414.xlsx
@@ -1614,7 +1614,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311029906</t>
+          <t xml:space="preserve">311029870</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Grontmij A/S (Glostrup)</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311197615</t>
+          <t xml:space="preserve">311197614</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Orbicon A/S</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306649</t>
+          <t xml:space="preserve">311306645</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Orbicon A/S</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
